--- a/artfynd/A 26089-2024 artfynd.xlsx
+++ b/artfynd/A 26089-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -897,6 +897,1643 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120403757</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78187</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>353</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Arjeplog, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>625784</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7332766</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120403751</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78278</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Arjeplog, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>626087</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7332871</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120403759</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78187</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>353</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Arjeplog, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>625963</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7332633</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120403740</v>
+      </c>
+      <c r="B7" t="n">
+        <v>89650</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Arjeplog, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>626010</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7332796</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120403753</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78278</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Arjeplog, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>626012</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7332797</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120403748</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78279</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Arjeplog, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>626004</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7332686</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120403746</v>
+      </c>
+      <c r="B10" t="n">
+        <v>56532</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Arjeplog, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>625839</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7332800</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120403745</v>
+      </c>
+      <c r="B11" t="n">
+        <v>89292</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Arjeplog, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>626005</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7332687</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120403747</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78279</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Arjeplog, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>626012</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7332797</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120403754</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78278</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Arjeplog, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>626005</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7332708</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120403755</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78278</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Arjeplog, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>626005</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7332686</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120403737</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79160</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Arjeplog, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>625834</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7332799</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120403738</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79160</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Arjeplog, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>626053</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7332836</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120403734</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90506</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>3242</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vitplätt</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Chaetodermella luna</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Arjeplog, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>626022</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7332776</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120403742</v>
+      </c>
+      <c r="B18" t="n">
+        <v>89650</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Arjeplog, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>626003</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7332701</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120403756</v>
+      </c>
+      <c r="B19" t="n">
+        <v>90730</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Arjeplog, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>625878</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7332849</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26089-2024 artfynd.xlsx
+++ b/artfynd/A 26089-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2534,6 +2534,2556 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120413464</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79160</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>NÖ Gålggåmisvárre, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>625705</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7332797</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120413492</v>
+      </c>
+      <c r="B21" t="n">
+        <v>77474</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>NÖ Gålggåmisvárre, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>625705</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7332799</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120413490</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79658</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>NÖ Gålggåmisvárre, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>625853</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7332733</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120413494</v>
+      </c>
+      <c r="B23" t="n">
+        <v>77926</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>NÖ Gålggåmisvárre, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>625730</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7332818</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120413474</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79652</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>NÖ Gålggåmisvárre, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>625828</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7332701</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120413465</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79160</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>NÖ Gålggåmisvárre, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>625854</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7332729</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120413470</v>
+      </c>
+      <c r="B26" t="n">
+        <v>89650</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>NÖ Gålggåmisvárre, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>625715</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7332825</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120413488</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78187</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>353</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>NÖ Gålggåmisvárre, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>625806</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7332495</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120413472</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57473</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>NÖ Gålggåmisvárre, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>625812</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7332656</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120413476</v>
+      </c>
+      <c r="B29" t="n">
+        <v>92048</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>NÖ Gålggåmisvárre, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>625812</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7332547</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120413485</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78187</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>353</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>NÖ Gålggåmisvárre, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>625700</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7332818</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120413473</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79652</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>NÖ Gålggåmisvárre, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>625875</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7332742</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120413477</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79659</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>NÖ Gålggåmisvárre, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>625858</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7332733</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120413471</v>
+      </c>
+      <c r="B33" t="n">
+        <v>89650</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>NÖ Gålggåmisvárre, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>625815</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7332543</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120413481</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78278</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>NÖ Gålggåmisvárre, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>625729</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7332823</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120413475</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91862</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>NÖ Gålggåmisvárre, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>625802</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7332542</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120413469</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79131</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>NÖ Gålggåmisvárre, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>625798</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7332635</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120413482</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78278</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>NÖ Gålggåmisvárre, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>625810</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7332539</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120413495</v>
+      </c>
+      <c r="B38" t="n">
+        <v>77926</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>NÖ Gålggåmisvárre, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>625813</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7332838</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120413493</v>
+      </c>
+      <c r="B39" t="n">
+        <v>77474</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>NÖ Gålggåmisvárre, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>625812</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7332838</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>120413480</v>
+      </c>
+      <c r="B40" t="n">
+        <v>78278</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>NÖ Gålggåmisvárre, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>625700</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7332827</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>120413491</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79658</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>NÖ Gålggåmisvárre, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>625877</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7332740</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>120413467</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79160</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>NÖ Gålggåmisvárre, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>625806</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7332496</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>120413479</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78278</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>NÖ Gålggåmisvárre, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>625716</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7332805</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>120413486</v>
+      </c>
+      <c r="B44" t="n">
+        <v>78187</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>353</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>NÖ Gålggåmisvárre, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>625706</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7332827</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26089-2024 artfynd.xlsx
+++ b/artfynd/A 26089-2024 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120403757</v>
+        <v>120403745</v>
       </c>
       <c r="B4" t="n">
-        <v>78187</v>
+        <v>89292</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>625784</v>
+        <v>626005</v>
       </c>
       <c r="R4" t="n">
-        <v>7332766</v>
+        <v>7332687</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1001,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120403751</v>
+        <v>120403754</v>
       </c>
       <c r="B5" t="n">
         <v>78278</v>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626087</v>
+        <v>626005</v>
       </c>
       <c r="R5" t="n">
-        <v>7332871</v>
+        <v>7332708</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120403759</v>
+        <v>120403748</v>
       </c>
       <c r="B6" t="n">
-        <v>78187</v>
+        <v>78279</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>625963</v>
+        <v>626004</v>
       </c>
       <c r="R6" t="n">
-        <v>7332633</v>
+        <v>7332686</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120403740</v>
+        <v>120403759</v>
       </c>
       <c r="B7" t="n">
-        <v>89650</v>
+        <v>78187</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626010</v>
+        <v>625963</v>
       </c>
       <c r="R7" t="n">
-        <v>7332796</v>
+        <v>7332633</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120403753</v>
+        <v>120403746</v>
       </c>
       <c r="B8" t="n">
-        <v>78278</v>
+        <v>56532</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,25 +1319,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626012</v>
+        <v>625839</v>
       </c>
       <c r="R8" t="n">
-        <v>7332797</v>
+        <v>7332800</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1383,6 +1383,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120403748</v>
+        <v>120403738</v>
       </c>
       <c r="B9" t="n">
-        <v>78279</v>
+        <v>79160</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626004</v>
+        <v>626053</v>
       </c>
       <c r="R9" t="n">
-        <v>7332686</v>
+        <v>7332836</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1511,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120403746</v>
+        <v>120403757</v>
       </c>
       <c r="B10" t="n">
-        <v>56532</v>
+        <v>78187</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1523,25 +1528,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>625839</v>
+        <v>625784</v>
       </c>
       <c r="R10" t="n">
-        <v>7332800</v>
+        <v>7332766</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1587,11 +1592,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120403745</v>
+        <v>120403753</v>
       </c>
       <c r="B11" t="n">
-        <v>89292</v>
+        <v>78278</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1630,25 +1630,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6286</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626005</v>
+        <v>626012</v>
       </c>
       <c r="R11" t="n">
-        <v>7332687</v>
+        <v>7332797</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120403747</v>
+        <v>120403742</v>
       </c>
       <c r="B12" t="n">
-        <v>78279</v>
+        <v>89650</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626012</v>
+        <v>626003</v>
       </c>
       <c r="R12" t="n">
-        <v>7332797</v>
+        <v>7332701</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120403754</v>
+        <v>120403734</v>
       </c>
       <c r="B13" t="n">
-        <v>78278</v>
+        <v>90506</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1838,21 +1838,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>3242</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626005</v>
+        <v>626022</v>
       </c>
       <c r="R13" t="n">
-        <v>7332708</v>
+        <v>7332776</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1924,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120403755</v>
+        <v>120403737</v>
       </c>
       <c r="B14" t="n">
-        <v>78278</v>
+        <v>79160</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1940,21 +1940,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626005</v>
+        <v>625834</v>
       </c>
       <c r="R14" t="n">
-        <v>7332686</v>
+        <v>7332799</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2026,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120403737</v>
+        <v>120403751</v>
       </c>
       <c r="B15" t="n">
-        <v>79160</v>
+        <v>78278</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2042,21 +2042,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2066,10 +2066,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>625834</v>
+        <v>626087</v>
       </c>
       <c r="R15" t="n">
-        <v>7332799</v>
+        <v>7332871</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2128,10 +2128,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120403738</v>
+        <v>120403740</v>
       </c>
       <c r="B16" t="n">
-        <v>79160</v>
+        <v>89650</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2144,21 +2144,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626053</v>
+        <v>626010</v>
       </c>
       <c r="R16" t="n">
-        <v>7332836</v>
+        <v>7332796</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2230,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120403734</v>
+        <v>120403755</v>
       </c>
       <c r="B17" t="n">
-        <v>90506</v>
+        <v>78278</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2246,21 +2246,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3242</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626022</v>
+        <v>626005</v>
       </c>
       <c r="R17" t="n">
-        <v>7332776</v>
+        <v>7332686</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2332,10 +2332,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120403742</v>
+        <v>120403747</v>
       </c>
       <c r="B18" t="n">
-        <v>89650</v>
+        <v>78279</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2348,21 +2348,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626003</v>
+        <v>626012</v>
       </c>
       <c r="R18" t="n">
-        <v>7332701</v>
+        <v>7332797</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120413464</v>
+        <v>120413471</v>
       </c>
       <c r="B20" t="n">
-        <v>79160</v>
+        <v>89650</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2552,21 +2552,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>625705</v>
+        <v>625815</v>
       </c>
       <c r="R20" t="n">
-        <v>7332797</v>
+        <v>7332543</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2638,10 +2638,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120413492</v>
+        <v>120413464</v>
       </c>
       <c r="B21" t="n">
-        <v>77474</v>
+        <v>79160</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2654,21 +2654,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2681,7 +2681,7 @@
         <v>625705</v>
       </c>
       <c r="R21" t="n">
-        <v>7332799</v>
+        <v>7332797</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2740,10 +2740,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120413490</v>
+        <v>120413475</v>
       </c>
       <c r="B22" t="n">
-        <v>79658</v>
+        <v>91862</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2752,25 +2752,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>4365</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2780,10 +2780,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>625853</v>
+        <v>625802</v>
       </c>
       <c r="R22" t="n">
-        <v>7332733</v>
+        <v>7332542</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2842,10 +2842,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120413494</v>
+        <v>120413479</v>
       </c>
       <c r="B23" t="n">
-        <v>77926</v>
+        <v>78278</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2858,21 +2858,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2882,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>625730</v>
+        <v>625716</v>
       </c>
       <c r="R23" t="n">
-        <v>7332818</v>
+        <v>7332805</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2944,10 +2944,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120413474</v>
+        <v>120413469</v>
       </c>
       <c r="B24" t="n">
-        <v>79652</v>
+        <v>79131</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2956,25 +2956,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>625828</v>
+        <v>625798</v>
       </c>
       <c r="R24" t="n">
-        <v>7332701</v>
+        <v>7332635</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3046,10 +3046,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120413465</v>
+        <v>120413481</v>
       </c>
       <c r="B25" t="n">
-        <v>79160</v>
+        <v>78278</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3062,21 +3062,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>625854</v>
+        <v>625729</v>
       </c>
       <c r="R25" t="n">
-        <v>7332729</v>
+        <v>7332823</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3148,10 +3148,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120413470</v>
+        <v>120413490</v>
       </c>
       <c r="B26" t="n">
-        <v>89650</v>
+        <v>79658</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3160,25 +3160,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1962</v>
+        <v>6463</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>625715</v>
+        <v>625853</v>
       </c>
       <c r="R26" t="n">
-        <v>7332825</v>
+        <v>7332733</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3250,10 +3250,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120413488</v>
+        <v>120413476</v>
       </c>
       <c r="B27" t="n">
-        <v>78187</v>
+        <v>92048</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3266,21 +3266,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>625806</v>
+        <v>625812</v>
       </c>
       <c r="R27" t="n">
-        <v>7332495</v>
+        <v>7332547</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3454,10 +3454,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120413476</v>
+        <v>120413486</v>
       </c>
       <c r="B29" t="n">
-        <v>92048</v>
+        <v>78187</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3470,21 +3470,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3494,10 +3494,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>625812</v>
+        <v>625706</v>
       </c>
       <c r="R29" t="n">
-        <v>7332547</v>
+        <v>7332827</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3658,10 +3658,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120413473</v>
+        <v>120413470</v>
       </c>
       <c r="B31" t="n">
-        <v>79652</v>
+        <v>89650</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3670,25 +3670,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>1962</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>625875</v>
+        <v>625715</v>
       </c>
       <c r="R31" t="n">
-        <v>7332742</v>
+        <v>7332825</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3760,10 +3760,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120413477</v>
+        <v>120413495</v>
       </c>
       <c r="B32" t="n">
-        <v>79659</v>
+        <v>77926</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3772,25 +3772,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6464</v>
+        <v>6437</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>625858</v>
+        <v>625813</v>
       </c>
       <c r="R32" t="n">
-        <v>7332733</v>
+        <v>7332838</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3862,10 +3862,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120413471</v>
+        <v>120413467</v>
       </c>
       <c r="B33" t="n">
-        <v>89650</v>
+        <v>79160</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3878,21 +3878,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>625815</v>
+        <v>625806</v>
       </c>
       <c r="R33" t="n">
-        <v>7332543</v>
+        <v>7332496</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3964,10 +3964,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120413481</v>
+        <v>120413477</v>
       </c>
       <c r="B34" t="n">
-        <v>78278</v>
+        <v>79659</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3976,25 +3976,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6464</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>625729</v>
+        <v>625858</v>
       </c>
       <c r="R34" t="n">
-        <v>7332823</v>
+        <v>7332733</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4066,10 +4066,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120413475</v>
+        <v>120413480</v>
       </c>
       <c r="B35" t="n">
-        <v>91862</v>
+        <v>78278</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4078,25 +4078,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4365</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>625802</v>
+        <v>625700</v>
       </c>
       <c r="R35" t="n">
-        <v>7332542</v>
+        <v>7332827</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4168,10 +4168,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120413469</v>
+        <v>120413494</v>
       </c>
       <c r="B36" t="n">
-        <v>79131</v>
+        <v>77926</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4184,21 +4184,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>625798</v>
+        <v>625730</v>
       </c>
       <c r="R36" t="n">
-        <v>7332635</v>
+        <v>7332818</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4270,10 +4270,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120413482</v>
+        <v>120413487</v>
       </c>
       <c r="B37" t="n">
-        <v>78278</v>
+        <v>78187</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4286,21 +4286,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>625810</v>
+        <v>625806</v>
       </c>
       <c r="R37" t="n">
-        <v>7332539</v>
+        <v>7332495</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4372,10 +4372,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120413495</v>
+        <v>120413492</v>
       </c>
       <c r="B38" t="n">
-        <v>77926</v>
+        <v>77474</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4388,21 +4388,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6437</v>
+        <v>6487</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>625813</v>
+        <v>625705</v>
       </c>
       <c r="R38" t="n">
-        <v>7332838</v>
+        <v>7332799</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4474,10 +4474,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120413493</v>
+        <v>120413474</v>
       </c>
       <c r="B39" t="n">
-        <v>77474</v>
+        <v>79652</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4486,25 +4486,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6487</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>625812</v>
+        <v>625828</v>
       </c>
       <c r="R39" t="n">
-        <v>7332838</v>
+        <v>7332701</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4576,10 +4576,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120413480</v>
+        <v>120413493</v>
       </c>
       <c r="B40" t="n">
-        <v>78278</v>
+        <v>77474</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4592,21 +4592,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4616,10 +4616,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>625700</v>
+        <v>625812</v>
       </c>
       <c r="R40" t="n">
-        <v>7332827</v>
+        <v>7332838</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4678,10 +4678,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120413491</v>
+        <v>120413473</v>
       </c>
       <c r="B41" t="n">
-        <v>79658</v>
+        <v>79652</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4694,21 +4694,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4718,10 +4718,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>625877</v>
+        <v>625875</v>
       </c>
       <c r="R41" t="n">
-        <v>7332740</v>
+        <v>7332742</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4780,7 +4780,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120413467</v>
+        <v>120413465</v>
       </c>
       <c r="B42" t="n">
         <v>79160</v>
@@ -4820,10 +4820,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>625806</v>
+        <v>625854</v>
       </c>
       <c r="R42" t="n">
-        <v>7332496</v>
+        <v>7332729</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120413479</v>
+        <v>120413482</v>
       </c>
       <c r="B43" t="n">
         <v>78278</v>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>625716</v>
+        <v>625810</v>
       </c>
       <c r="R43" t="n">
-        <v>7332805</v>
+        <v>7332539</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4984,10 +4984,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120413486</v>
+        <v>120413491</v>
       </c>
       <c r="B44" t="n">
-        <v>78187</v>
+        <v>79658</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4996,25 +4996,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5024,10 +5024,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>625706</v>
+        <v>625877</v>
       </c>
       <c r="R44" t="n">
-        <v>7332827</v>
+        <v>7332740</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 26089-2024 artfynd.xlsx
+++ b/artfynd/A 26089-2024 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120403745</v>
+        <v>120403748</v>
       </c>
       <c r="B4" t="n">
-        <v>89292</v>
+        <v>78279</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6286</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626005</v>
+        <v>626004</v>
       </c>
       <c r="R4" t="n">
-        <v>7332687</v>
+        <v>7332686</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1001,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120403754</v>
+        <v>120403751</v>
       </c>
       <c r="B5" t="n">
         <v>78278</v>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626005</v>
+        <v>626087</v>
       </c>
       <c r="R5" t="n">
-        <v>7332708</v>
+        <v>7332871</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120403748</v>
+        <v>120403747</v>
       </c>
       <c r="B6" t="n">
         <v>78279</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626004</v>
+        <v>626012</v>
       </c>
       <c r="R6" t="n">
-        <v>7332686</v>
+        <v>7332797</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120403759</v>
+        <v>120403742</v>
       </c>
       <c r="B7" t="n">
-        <v>78187</v>
+        <v>89650</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>625963</v>
+        <v>626003</v>
       </c>
       <c r="R7" t="n">
-        <v>7332633</v>
+        <v>7332701</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120403746</v>
+        <v>120403757</v>
       </c>
       <c r="B8" t="n">
-        <v>56532</v>
+        <v>78187</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,25 +1319,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>625839</v>
+        <v>625784</v>
       </c>
       <c r="R8" t="n">
-        <v>7332800</v>
+        <v>7332766</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1383,11 +1383,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,7 +1409,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120403738</v>
+        <v>120403737</v>
       </c>
       <c r="B9" t="n">
         <v>79160</v>
@@ -1454,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626053</v>
+        <v>625834</v>
       </c>
       <c r="R9" t="n">
-        <v>7332836</v>
+        <v>7332799</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1516,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120403757</v>
+        <v>120403755</v>
       </c>
       <c r="B10" t="n">
-        <v>78187</v>
+        <v>78278</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>625784</v>
+        <v>626005</v>
       </c>
       <c r="R10" t="n">
-        <v>7332766</v>
+        <v>7332686</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1618,7 +1613,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120403753</v>
+        <v>120403754</v>
       </c>
       <c r="B11" t="n">
         <v>78278</v>
@@ -1658,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626012</v>
+        <v>626005</v>
       </c>
       <c r="R11" t="n">
-        <v>7332797</v>
+        <v>7332708</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1720,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120403742</v>
+        <v>120403745</v>
       </c>
       <c r="B12" t="n">
-        <v>89650</v>
+        <v>89292</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1732,25 +1727,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1962</v>
+        <v>6286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626003</v>
+        <v>626005</v>
       </c>
       <c r="R12" t="n">
-        <v>7332701</v>
+        <v>7332687</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1822,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120403734</v>
+        <v>120403759</v>
       </c>
       <c r="B13" t="n">
-        <v>90506</v>
+        <v>78187</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1838,21 +1833,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3242</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626022</v>
+        <v>625963</v>
       </c>
       <c r="R13" t="n">
-        <v>7332776</v>
+        <v>7332633</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1924,7 +1919,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120403737</v>
+        <v>120403738</v>
       </c>
       <c r="B14" t="n">
         <v>79160</v>
@@ -1964,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>625834</v>
+        <v>626053</v>
       </c>
       <c r="R14" t="n">
-        <v>7332799</v>
+        <v>7332836</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2026,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120403751</v>
+        <v>120403746</v>
       </c>
       <c r="B15" t="n">
-        <v>78278</v>
+        <v>56532</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2038,25 +2033,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2066,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626087</v>
+        <v>625839</v>
       </c>
       <c r="R15" t="n">
-        <v>7332871</v>
+        <v>7332800</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2102,6 +2097,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2230,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120403755</v>
+        <v>120403756</v>
       </c>
       <c r="B17" t="n">
-        <v>78278</v>
+        <v>90730</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2242,25 +2242,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626005</v>
+        <v>625878</v>
       </c>
       <c r="R17" t="n">
-        <v>7332686</v>
+        <v>7332849</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2332,10 +2332,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120403747</v>
+        <v>120403753</v>
       </c>
       <c r="B18" t="n">
-        <v>78279</v>
+        <v>78278</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2348,21 +2348,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120403756</v>
+        <v>120403734</v>
       </c>
       <c r="B19" t="n">
-        <v>90730</v>
+        <v>90506</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2446,25 +2446,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1503</v>
+        <v>3242</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>625878</v>
+        <v>626022</v>
       </c>
       <c r="R19" t="n">
-        <v>7332849</v>
+        <v>7332776</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120413471</v>
+        <v>120413491</v>
       </c>
       <c r="B20" t="n">
-        <v>89650</v>
+        <v>79658</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2548,25 +2548,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1962</v>
+        <v>6463</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>625815</v>
+        <v>625877</v>
       </c>
       <c r="R20" t="n">
-        <v>7332543</v>
+        <v>7332740</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2638,10 +2638,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120413464</v>
+        <v>120413494</v>
       </c>
       <c r="B21" t="n">
-        <v>79160</v>
+        <v>77926</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2654,21 +2654,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>625705</v>
+        <v>625730</v>
       </c>
       <c r="R21" t="n">
-        <v>7332797</v>
+        <v>7332818</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2740,10 +2740,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120413475</v>
+        <v>120413486</v>
       </c>
       <c r="B22" t="n">
-        <v>91862</v>
+        <v>78187</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2752,25 +2752,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4365</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2780,10 +2780,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>625802</v>
+        <v>625706</v>
       </c>
       <c r="R22" t="n">
-        <v>7332542</v>
+        <v>7332827</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2842,7 +2842,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120413479</v>
+        <v>120413482</v>
       </c>
       <c r="B23" t="n">
         <v>78278</v>
@@ -2882,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>625716</v>
+        <v>625810</v>
       </c>
       <c r="R23" t="n">
-        <v>7332805</v>
+        <v>7332539</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3046,10 +3046,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120413481</v>
+        <v>120413465</v>
       </c>
       <c r="B25" t="n">
-        <v>78278</v>
+        <v>79160</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3062,21 +3062,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>625729</v>
+        <v>625854</v>
       </c>
       <c r="R25" t="n">
-        <v>7332823</v>
+        <v>7332729</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3148,10 +3148,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120413490</v>
+        <v>120413475</v>
       </c>
       <c r="B26" t="n">
-        <v>79658</v>
+        <v>91862</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3160,25 +3160,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6463</v>
+        <v>4365</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>625853</v>
+        <v>625802</v>
       </c>
       <c r="R26" t="n">
-        <v>7332733</v>
+        <v>7332542</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3250,10 +3250,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120413476</v>
+        <v>120413471</v>
       </c>
       <c r="B27" t="n">
-        <v>92048</v>
+        <v>89650</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3266,21 +3266,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>625812</v>
+        <v>625815</v>
       </c>
       <c r="R27" t="n">
-        <v>7332547</v>
+        <v>7332543</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3352,10 +3352,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120413472</v>
+        <v>120413473</v>
       </c>
       <c r="B28" t="n">
-        <v>57473</v>
+        <v>79652</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3364,25 +3364,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>625812</v>
+        <v>625875</v>
       </c>
       <c r="R28" t="n">
-        <v>7332656</v>
+        <v>7332742</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3454,10 +3454,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120413486</v>
+        <v>120413493</v>
       </c>
       <c r="B29" t="n">
-        <v>78187</v>
+        <v>77474</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3470,21 +3470,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>6487</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3494,10 +3494,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>625706</v>
+        <v>625812</v>
       </c>
       <c r="R29" t="n">
-        <v>7332827</v>
+        <v>7332838</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3556,10 +3556,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120413485</v>
+        <v>120413495</v>
       </c>
       <c r="B30" t="n">
-        <v>78187</v>
+        <v>77926</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3572,21 +3572,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3596,10 +3596,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>625700</v>
+        <v>625813</v>
       </c>
       <c r="R30" t="n">
-        <v>7332818</v>
+        <v>7332838</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3658,10 +3658,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120413470</v>
+        <v>120413481</v>
       </c>
       <c r="B31" t="n">
-        <v>89650</v>
+        <v>78278</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3674,21 +3674,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>625715</v>
+        <v>625729</v>
       </c>
       <c r="R31" t="n">
-        <v>7332825</v>
+        <v>7332823</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3760,10 +3760,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120413495</v>
+        <v>120413476</v>
       </c>
       <c r="B32" t="n">
-        <v>77926</v>
+        <v>92048</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3776,21 +3776,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6437</v>
+        <v>2079</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>625813</v>
+        <v>625812</v>
       </c>
       <c r="R32" t="n">
-        <v>7332838</v>
+        <v>7332547</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3862,7 +3862,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120413467</v>
+        <v>120413464</v>
       </c>
       <c r="B33" t="n">
         <v>79160</v>
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>625806</v>
+        <v>625705</v>
       </c>
       <c r="R33" t="n">
-        <v>7332496</v>
+        <v>7332797</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3964,10 +3964,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120413477</v>
+        <v>120413488</v>
       </c>
       <c r="B34" t="n">
-        <v>79659</v>
+        <v>78187</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3976,25 +3976,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6464</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>625858</v>
+        <v>625806</v>
       </c>
       <c r="R34" t="n">
-        <v>7332733</v>
+        <v>7332495</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4066,10 +4066,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120413480</v>
+        <v>120413474</v>
       </c>
       <c r="B35" t="n">
-        <v>78278</v>
+        <v>79652</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4078,25 +4078,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>625700</v>
+        <v>625828</v>
       </c>
       <c r="R35" t="n">
-        <v>7332827</v>
+        <v>7332701</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4168,10 +4168,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120413494</v>
+        <v>120413479</v>
       </c>
       <c r="B36" t="n">
-        <v>77926</v>
+        <v>78278</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4184,21 +4184,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>625730</v>
+        <v>625716</v>
       </c>
       <c r="R36" t="n">
-        <v>7332818</v>
+        <v>7332805</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4270,10 +4270,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120413487</v>
+        <v>120413467</v>
       </c>
       <c r="B37" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4286,21 +4286,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4313,7 +4313,7 @@
         <v>625806</v>
       </c>
       <c r="R37" t="n">
-        <v>7332495</v>
+        <v>7332496</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4372,10 +4372,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120413492</v>
+        <v>120413477</v>
       </c>
       <c r="B38" t="n">
-        <v>77474</v>
+        <v>79659</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4384,25 +4384,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6487</v>
+        <v>6464</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>625705</v>
+        <v>625858</v>
       </c>
       <c r="R38" t="n">
-        <v>7332799</v>
+        <v>7332733</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4474,10 +4474,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120413474</v>
+        <v>120413470</v>
       </c>
       <c r="B39" t="n">
-        <v>79652</v>
+        <v>89650</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4486,25 +4486,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>1962</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>625828</v>
+        <v>625715</v>
       </c>
       <c r="R39" t="n">
-        <v>7332701</v>
+        <v>7332825</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4576,10 +4576,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120413493</v>
+        <v>120413485</v>
       </c>
       <c r="B40" t="n">
-        <v>77474</v>
+        <v>78187</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4592,21 +4592,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6487</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4616,10 +4616,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>625812</v>
+        <v>625700</v>
       </c>
       <c r="R40" t="n">
-        <v>7332838</v>
+        <v>7332818</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4678,10 +4678,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120413473</v>
+        <v>120413492</v>
       </c>
       <c r="B41" t="n">
-        <v>79652</v>
+        <v>77474</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4690,25 +4690,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>6487</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4718,10 +4718,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>625875</v>
+        <v>625705</v>
       </c>
       <c r="R41" t="n">
-        <v>7332742</v>
+        <v>7332799</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4780,10 +4780,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120413465</v>
+        <v>120413472</v>
       </c>
       <c r="B42" t="n">
-        <v>79160</v>
+        <v>57473</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4796,21 +4796,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4820,10 +4820,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>625854</v>
+        <v>625812</v>
       </c>
       <c r="R42" t="n">
-        <v>7332729</v>
+        <v>7332656</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4882,10 +4882,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120413482</v>
+        <v>120413490</v>
       </c>
       <c r="B43" t="n">
-        <v>78278</v>
+        <v>79658</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4894,25 +4894,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>625810</v>
+        <v>625853</v>
       </c>
       <c r="R43" t="n">
-        <v>7332539</v>
+        <v>7332733</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4984,10 +4984,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120413491</v>
+        <v>120413480</v>
       </c>
       <c r="B44" t="n">
-        <v>79658</v>
+        <v>78278</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4996,25 +4996,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5024,10 +5024,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>625877</v>
+        <v>625700</v>
       </c>
       <c r="R44" t="n">
-        <v>7332740</v>
+        <v>7332827</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 26089-2024 artfynd.xlsx
+++ b/artfynd/A 26089-2024 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120403748</v>
+        <v>120403737</v>
       </c>
       <c r="B4" t="n">
-        <v>78279</v>
+        <v>79160</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626004</v>
+        <v>625834</v>
       </c>
       <c r="R4" t="n">
-        <v>7332686</v>
+        <v>7332799</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120403751</v>
+        <v>120403757</v>
       </c>
       <c r="B5" t="n">
-        <v>78278</v>
+        <v>78187</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,21 +1017,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626087</v>
+        <v>625784</v>
       </c>
       <c r="R5" t="n">
-        <v>7332871</v>
+        <v>7332766</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120403742</v>
+        <v>120403755</v>
       </c>
       <c r="B7" t="n">
-        <v>89650</v>
+        <v>78278</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626003</v>
+        <v>626005</v>
       </c>
       <c r="R7" t="n">
-        <v>7332701</v>
+        <v>7332686</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120403757</v>
+        <v>120403745</v>
       </c>
       <c r="B8" t="n">
-        <v>78187</v>
+        <v>89292</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,25 +1319,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>625784</v>
+        <v>626005</v>
       </c>
       <c r="R8" t="n">
-        <v>7332766</v>
+        <v>7332687</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120403737</v>
+        <v>120403740</v>
       </c>
       <c r="B9" t="n">
-        <v>79160</v>
+        <v>89650</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>625834</v>
+        <v>626010</v>
       </c>
       <c r="R9" t="n">
-        <v>7332799</v>
+        <v>7332796</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1511,7 +1511,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120403755</v>
+        <v>120403754</v>
       </c>
       <c r="B10" t="n">
         <v>78278</v>
@@ -1554,7 +1554,7 @@
         <v>626005</v>
       </c>
       <c r="R10" t="n">
-        <v>7332686</v>
+        <v>7332708</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1613,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120403754</v>
+        <v>120403748</v>
       </c>
       <c r="B11" t="n">
-        <v>78278</v>
+        <v>78279</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626005</v>
+        <v>626004</v>
       </c>
       <c r="R11" t="n">
-        <v>7332708</v>
+        <v>7332686</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1715,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120403745</v>
+        <v>120403734</v>
       </c>
       <c r="B12" t="n">
-        <v>89292</v>
+        <v>90506</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1727,25 +1727,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6286</v>
+        <v>3242</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626005</v>
+        <v>626022</v>
       </c>
       <c r="R12" t="n">
-        <v>7332687</v>
+        <v>7332776</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1817,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120403759</v>
+        <v>120403753</v>
       </c>
       <c r="B13" t="n">
-        <v>78187</v>
+        <v>78278</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1833,21 +1833,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>625963</v>
+        <v>626012</v>
       </c>
       <c r="R13" t="n">
-        <v>7332633</v>
+        <v>7332797</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1919,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120403738</v>
+        <v>120403751</v>
       </c>
       <c r="B14" t="n">
-        <v>79160</v>
+        <v>78278</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,21 +1935,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626053</v>
+        <v>626087</v>
       </c>
       <c r="R14" t="n">
-        <v>7332836</v>
+        <v>7332871</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120403746</v>
+        <v>120403759</v>
       </c>
       <c r="B15" t="n">
-        <v>56532</v>
+        <v>78187</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2033,25 +2033,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>625839</v>
+        <v>625963</v>
       </c>
       <c r="R15" t="n">
-        <v>7332800</v>
+        <v>7332633</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2097,11 +2097,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2128,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120403740</v>
+        <v>120403738</v>
       </c>
       <c r="B16" t="n">
-        <v>89650</v>
+        <v>79160</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2144,21 +2139,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2168,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626010</v>
+        <v>626053</v>
       </c>
       <c r="R16" t="n">
-        <v>7332796</v>
+        <v>7332836</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2332,10 +2327,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120403753</v>
+        <v>120403746</v>
       </c>
       <c r="B18" t="n">
-        <v>78278</v>
+        <v>56532</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2344,25 +2339,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2372,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626012</v>
+        <v>625839</v>
       </c>
       <c r="R18" t="n">
-        <v>7332797</v>
+        <v>7332800</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2408,6 +2403,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2434,10 +2434,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120403734</v>
+        <v>120403742</v>
       </c>
       <c r="B19" t="n">
-        <v>90506</v>
+        <v>89650</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2450,21 +2450,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3242</v>
+        <v>1962</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626022</v>
+        <v>626003</v>
       </c>
       <c r="R19" t="n">
-        <v>7332776</v>
+        <v>7332701</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120413491</v>
+        <v>120413469</v>
       </c>
       <c r="B20" t="n">
-        <v>79658</v>
+        <v>79131</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2548,25 +2548,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>625877</v>
+        <v>625798</v>
       </c>
       <c r="R20" t="n">
-        <v>7332740</v>
+        <v>7332635</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2638,10 +2638,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120413494</v>
+        <v>120413487</v>
       </c>
       <c r="B21" t="n">
-        <v>77926</v>
+        <v>78187</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2654,21 +2654,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>625730</v>
+        <v>625806</v>
       </c>
       <c r="R21" t="n">
-        <v>7332818</v>
+        <v>7332495</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2740,10 +2740,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120413486</v>
+        <v>120413482</v>
       </c>
       <c r="B22" t="n">
-        <v>78187</v>
+        <v>78278</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2756,21 +2756,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2780,10 +2780,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>625706</v>
+        <v>625810</v>
       </c>
       <c r="R22" t="n">
-        <v>7332827</v>
+        <v>7332539</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2842,10 +2842,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120413482</v>
+        <v>120413486</v>
       </c>
       <c r="B23" t="n">
-        <v>78278</v>
+        <v>78187</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2858,21 +2858,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2882,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>625810</v>
+        <v>625706</v>
       </c>
       <c r="R23" t="n">
-        <v>7332539</v>
+        <v>7332827</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2944,10 +2944,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120413469</v>
+        <v>120413470</v>
       </c>
       <c r="B24" t="n">
-        <v>79131</v>
+        <v>89650</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2960,21 +2960,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>1962</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>625798</v>
+        <v>625715</v>
       </c>
       <c r="R24" t="n">
-        <v>7332635</v>
+        <v>7332825</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3046,10 +3046,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120413465</v>
+        <v>120413490</v>
       </c>
       <c r="B25" t="n">
-        <v>79160</v>
+        <v>79658</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3058,25 +3058,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6463</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>625854</v>
+        <v>625853</v>
       </c>
       <c r="R25" t="n">
-        <v>7332729</v>
+        <v>7332733</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3148,10 +3148,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120413475</v>
+        <v>120413485</v>
       </c>
       <c r="B26" t="n">
-        <v>91862</v>
+        <v>78187</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3160,25 +3160,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4365</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>625802</v>
+        <v>625700</v>
       </c>
       <c r="R26" t="n">
-        <v>7332542</v>
+        <v>7332818</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3250,10 +3250,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120413471</v>
+        <v>120413475</v>
       </c>
       <c r="B27" t="n">
-        <v>89650</v>
+        <v>91862</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3262,25 +3262,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1962</v>
+        <v>4365</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>625815</v>
+        <v>625802</v>
       </c>
       <c r="R27" t="n">
-        <v>7332543</v>
+        <v>7332542</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3352,10 +3352,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120413473</v>
+        <v>120413493</v>
       </c>
       <c r="B28" t="n">
-        <v>79652</v>
+        <v>77474</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3364,25 +3364,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>6487</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>625875</v>
+        <v>625812</v>
       </c>
       <c r="R28" t="n">
-        <v>7332742</v>
+        <v>7332838</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3454,10 +3454,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120413493</v>
+        <v>120413465</v>
       </c>
       <c r="B29" t="n">
-        <v>77474</v>
+        <v>79160</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3470,21 +3470,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3494,10 +3494,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>625812</v>
+        <v>625854</v>
       </c>
       <c r="R29" t="n">
-        <v>7332838</v>
+        <v>7332729</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3556,10 +3556,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120413495</v>
+        <v>120413480</v>
       </c>
       <c r="B30" t="n">
-        <v>77926</v>
+        <v>78278</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3572,21 +3572,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3596,10 +3596,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>625813</v>
+        <v>625700</v>
       </c>
       <c r="R30" t="n">
-        <v>7332838</v>
+        <v>7332827</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3658,10 +3658,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120413481</v>
+        <v>120413491</v>
       </c>
       <c r="B31" t="n">
-        <v>78278</v>
+        <v>79658</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3670,25 +3670,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6463</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>625729</v>
+        <v>625877</v>
       </c>
       <c r="R31" t="n">
-        <v>7332823</v>
+        <v>7332740</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3760,10 +3760,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120413476</v>
+        <v>120413473</v>
       </c>
       <c r="B32" t="n">
-        <v>92048</v>
+        <v>79652</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3772,25 +3772,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2079</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>625812</v>
+        <v>625875</v>
       </c>
       <c r="R32" t="n">
-        <v>7332547</v>
+        <v>7332742</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3862,10 +3862,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120413464</v>
+        <v>120413481</v>
       </c>
       <c r="B33" t="n">
-        <v>79160</v>
+        <v>78278</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3878,21 +3878,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>625705</v>
+        <v>625729</v>
       </c>
       <c r="R33" t="n">
-        <v>7332797</v>
+        <v>7332823</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3964,10 +3964,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120413488</v>
+        <v>120413494</v>
       </c>
       <c r="B34" t="n">
-        <v>78187</v>
+        <v>77926</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3980,21 +3980,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>625806</v>
+        <v>625730</v>
       </c>
       <c r="R34" t="n">
-        <v>7332495</v>
+        <v>7332818</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4066,10 +4066,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120413474</v>
+        <v>120413467</v>
       </c>
       <c r="B35" t="n">
-        <v>79652</v>
+        <v>79160</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4078,25 +4078,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>625828</v>
+        <v>625806</v>
       </c>
       <c r="R35" t="n">
-        <v>7332701</v>
+        <v>7332496</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4168,10 +4168,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120413479</v>
+        <v>120413471</v>
       </c>
       <c r="B36" t="n">
-        <v>78278</v>
+        <v>89650</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4184,21 +4184,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>625716</v>
+        <v>625815</v>
       </c>
       <c r="R36" t="n">
-        <v>7332805</v>
+        <v>7332543</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4270,10 +4270,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120413467</v>
+        <v>120413479</v>
       </c>
       <c r="B37" t="n">
-        <v>79160</v>
+        <v>78278</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4286,21 +4286,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>625806</v>
+        <v>625716</v>
       </c>
       <c r="R37" t="n">
-        <v>7332496</v>
+        <v>7332805</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4372,10 +4372,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120413477</v>
+        <v>120413495</v>
       </c>
       <c r="B38" t="n">
-        <v>79659</v>
+        <v>77926</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4384,25 +4384,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6464</v>
+        <v>6437</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>625858</v>
+        <v>625813</v>
       </c>
       <c r="R38" t="n">
-        <v>7332733</v>
+        <v>7332838</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4474,10 +4474,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120413470</v>
+        <v>120413476</v>
       </c>
       <c r="B39" t="n">
-        <v>89650</v>
+        <v>92048</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4490,21 +4490,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1962</v>
+        <v>2079</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>625715</v>
+        <v>625812</v>
       </c>
       <c r="R39" t="n">
-        <v>7332825</v>
+        <v>7332547</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4576,10 +4576,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120413485</v>
+        <v>120413472</v>
       </c>
       <c r="B40" t="n">
-        <v>78187</v>
+        <v>57473</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4592,21 +4592,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4616,10 +4616,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>625700</v>
+        <v>625812</v>
       </c>
       <c r="R40" t="n">
-        <v>7332818</v>
+        <v>7332656</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4678,10 +4678,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120413492</v>
+        <v>120413474</v>
       </c>
       <c r="B41" t="n">
-        <v>77474</v>
+        <v>79652</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4690,25 +4690,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6487</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4718,10 +4718,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>625705</v>
+        <v>625828</v>
       </c>
       <c r="R41" t="n">
-        <v>7332799</v>
+        <v>7332701</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4780,10 +4780,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120413472</v>
+        <v>120413492</v>
       </c>
       <c r="B42" t="n">
-        <v>57473</v>
+        <v>77474</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4796,21 +4796,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>6487</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4820,10 +4820,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>625812</v>
+        <v>625705</v>
       </c>
       <c r="R42" t="n">
-        <v>7332656</v>
+        <v>7332799</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4882,10 +4882,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120413490</v>
+        <v>120413477</v>
       </c>
       <c r="B43" t="n">
-        <v>79658</v>
+        <v>79659</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4898,21 +4898,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4922,7 +4922,7 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>625853</v>
+        <v>625858</v>
       </c>
       <c r="R43" t="n">
         <v>7332733</v>
@@ -4984,10 +4984,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120413480</v>
+        <v>120413464</v>
       </c>
       <c r="B44" t="n">
-        <v>78278</v>
+        <v>79160</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5000,21 +5000,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5024,10 +5024,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>625700</v>
+        <v>625705</v>
       </c>
       <c r="R44" t="n">
-        <v>7332827</v>
+        <v>7332797</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 26089-2024 artfynd.xlsx
+++ b/artfynd/A 26089-2024 artfynd.xlsx
@@ -1511,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120403754</v>
+        <v>120403748</v>
       </c>
       <c r="B10" t="n">
-        <v>78278</v>
+        <v>78279</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626005</v>
+        <v>626004</v>
       </c>
       <c r="R10" t="n">
-        <v>7332708</v>
+        <v>7332686</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1613,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120403748</v>
+        <v>120403754</v>
       </c>
       <c r="B11" t="n">
-        <v>78279</v>
+        <v>78278</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626004</v>
+        <v>626005</v>
       </c>
       <c r="R11" t="n">
-        <v>7332686</v>
+        <v>7332708</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -2842,10 +2842,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120413486</v>
+        <v>120413470</v>
       </c>
       <c r="B23" t="n">
-        <v>78187</v>
+        <v>89650</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2858,21 +2858,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2882,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>625706</v>
+        <v>625715</v>
       </c>
       <c r="R23" t="n">
-        <v>7332827</v>
+        <v>7332825</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2944,10 +2944,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120413470</v>
+        <v>120413486</v>
       </c>
       <c r="B24" t="n">
-        <v>89650</v>
+        <v>78187</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2960,21 +2960,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>625715</v>
+        <v>625706</v>
       </c>
       <c r="R24" t="n">
-        <v>7332825</v>
+        <v>7332827</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -4474,10 +4474,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120413476</v>
+        <v>120413474</v>
       </c>
       <c r="B39" t="n">
-        <v>92048</v>
+        <v>79652</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4486,25 +4486,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2079</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>625812</v>
+        <v>625828</v>
       </c>
       <c r="R39" t="n">
-        <v>7332547</v>
+        <v>7332701</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4678,10 +4678,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120413474</v>
+        <v>120413476</v>
       </c>
       <c r="B41" t="n">
-        <v>79652</v>
+        <v>92048</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4690,25 +4690,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>2079</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4718,10 +4718,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>625828</v>
+        <v>625812</v>
       </c>
       <c r="R41" t="n">
-        <v>7332701</v>
+        <v>7332547</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 26089-2024 artfynd.xlsx
+++ b/artfynd/A 26089-2024 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120403737</v>
+        <v>120403757</v>
       </c>
       <c r="B4" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>625834</v>
+        <v>625784</v>
       </c>
       <c r="R4" t="n">
-        <v>7332799</v>
+        <v>7332766</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120403757</v>
+        <v>120403753</v>
       </c>
       <c r="B5" t="n">
-        <v>78187</v>
+        <v>78278</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,21 +1017,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>625784</v>
+        <v>626012</v>
       </c>
       <c r="R5" t="n">
-        <v>7332766</v>
+        <v>7332797</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120403747</v>
+        <v>120403751</v>
       </c>
       <c r="B6" t="n">
-        <v>78279</v>
+        <v>78278</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626012</v>
+        <v>626087</v>
       </c>
       <c r="R6" t="n">
-        <v>7332797</v>
+        <v>7332871</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120403755</v>
+        <v>120403759</v>
       </c>
       <c r="B7" t="n">
-        <v>78278</v>
+        <v>78187</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626005</v>
+        <v>625963</v>
       </c>
       <c r="R7" t="n">
-        <v>7332686</v>
+        <v>7332633</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120403745</v>
+        <v>120403756</v>
       </c>
       <c r="B8" t="n">
-        <v>89292</v>
+        <v>90730</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6286</v>
+        <v>1503</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626005</v>
+        <v>625878</v>
       </c>
       <c r="R8" t="n">
-        <v>7332687</v>
+        <v>7332849</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120403740</v>
+        <v>120403747</v>
       </c>
       <c r="B9" t="n">
-        <v>89650</v>
+        <v>78279</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626010</v>
+        <v>626012</v>
       </c>
       <c r="R9" t="n">
-        <v>7332796</v>
+        <v>7332797</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120403748</v>
+        <v>120403738</v>
       </c>
       <c r="B10" t="n">
-        <v>78279</v>
+        <v>79160</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626004</v>
+        <v>626053</v>
       </c>
       <c r="R10" t="n">
-        <v>7332686</v>
+        <v>7332836</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1613,7 +1613,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120403754</v>
+        <v>120403755</v>
       </c>
       <c r="B11" t="n">
         <v>78278</v>
@@ -1656,7 +1656,7 @@
         <v>626005</v>
       </c>
       <c r="R11" t="n">
-        <v>7332708</v>
+        <v>7332686</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1715,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120403734</v>
+        <v>120403754</v>
       </c>
       <c r="B12" t="n">
-        <v>90506</v>
+        <v>78278</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,21 +1731,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3242</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626022</v>
+        <v>626005</v>
       </c>
       <c r="R12" t="n">
-        <v>7332776</v>
+        <v>7332708</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1817,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120403753</v>
+        <v>120403746</v>
       </c>
       <c r="B13" t="n">
-        <v>78278</v>
+        <v>56532</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1829,25 +1829,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626012</v>
+        <v>625839</v>
       </c>
       <c r="R13" t="n">
-        <v>7332797</v>
+        <v>7332800</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1893,6 +1893,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1919,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120403751</v>
+        <v>120403748</v>
       </c>
       <c r="B14" t="n">
-        <v>78278</v>
+        <v>78279</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,21 +1940,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626087</v>
+        <v>626004</v>
       </c>
       <c r="R14" t="n">
-        <v>7332871</v>
+        <v>7332686</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2021,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120403759</v>
+        <v>120403745</v>
       </c>
       <c r="B15" t="n">
-        <v>78187</v>
+        <v>89292</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2033,25 +2038,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2066,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>625963</v>
+        <v>626005</v>
       </c>
       <c r="R15" t="n">
-        <v>7332633</v>
+        <v>7332687</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2123,7 +2128,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120403738</v>
+        <v>120403737</v>
       </c>
       <c r="B16" t="n">
         <v>79160</v>
@@ -2163,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626053</v>
+        <v>625834</v>
       </c>
       <c r="R16" t="n">
-        <v>7332836</v>
+        <v>7332799</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2225,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120403756</v>
+        <v>120403742</v>
       </c>
       <c r="B17" t="n">
-        <v>90730</v>
+        <v>89650</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2237,25 +2242,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1503</v>
+        <v>1962</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>625878</v>
+        <v>626003</v>
       </c>
       <c r="R17" t="n">
-        <v>7332849</v>
+        <v>7332701</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2327,10 +2332,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120403746</v>
+        <v>120403734</v>
       </c>
       <c r="B18" t="n">
-        <v>56532</v>
+        <v>90506</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2339,25 +2344,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>3242</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>625839</v>
+        <v>626022</v>
       </c>
       <c r="R18" t="n">
-        <v>7332800</v>
+        <v>7332776</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2403,11 +2408,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2434,7 +2434,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120403742</v>
+        <v>120403740</v>
       </c>
       <c r="B19" t="n">
         <v>89650</v>
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626003</v>
+        <v>626010</v>
       </c>
       <c r="R19" t="n">
-        <v>7332701</v>
+        <v>7332796</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120413469</v>
+        <v>120413470</v>
       </c>
       <c r="B20" t="n">
-        <v>79131</v>
+        <v>89650</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2552,21 +2552,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>1962</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>625798</v>
+        <v>625715</v>
       </c>
       <c r="R20" t="n">
-        <v>7332635</v>
+        <v>7332825</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2638,10 +2638,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120413487</v>
+        <v>120413475</v>
       </c>
       <c r="B21" t="n">
-        <v>78187</v>
+        <v>91862</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2650,25 +2650,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>4365</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>625806</v>
+        <v>625802</v>
       </c>
       <c r="R21" t="n">
-        <v>7332495</v>
+        <v>7332542</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2740,10 +2740,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120413482</v>
+        <v>120413467</v>
       </c>
       <c r="B22" t="n">
-        <v>78278</v>
+        <v>79160</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2756,21 +2756,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2780,10 +2780,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>625810</v>
+        <v>625806</v>
       </c>
       <c r="R22" t="n">
-        <v>7332539</v>
+        <v>7332496</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2842,10 +2842,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120413470</v>
+        <v>120413477</v>
       </c>
       <c r="B23" t="n">
-        <v>89650</v>
+        <v>79659</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2854,25 +2854,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1962</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2882,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>625715</v>
+        <v>625858</v>
       </c>
       <c r="R23" t="n">
-        <v>7332825</v>
+        <v>7332733</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2944,7 +2944,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120413486</v>
+        <v>120413485</v>
       </c>
       <c r="B24" t="n">
         <v>78187</v>
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>625706</v>
+        <v>625700</v>
       </c>
       <c r="R24" t="n">
-        <v>7332827</v>
+        <v>7332818</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3046,10 +3046,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120413490</v>
+        <v>120413495</v>
       </c>
       <c r="B25" t="n">
-        <v>79658</v>
+        <v>77926</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3058,25 +3058,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6463</v>
+        <v>6437</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>625853</v>
+        <v>625813</v>
       </c>
       <c r="R25" t="n">
-        <v>7332733</v>
+        <v>7332838</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3148,10 +3148,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120413485</v>
+        <v>120413491</v>
       </c>
       <c r="B26" t="n">
-        <v>78187</v>
+        <v>79658</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3160,25 +3160,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6463</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>625700</v>
+        <v>625877</v>
       </c>
       <c r="R26" t="n">
-        <v>7332818</v>
+        <v>7332740</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3250,10 +3250,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120413475</v>
+        <v>120413472</v>
       </c>
       <c r="B27" t="n">
-        <v>91862</v>
+        <v>57473</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3262,25 +3262,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4365</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>625802</v>
+        <v>625812</v>
       </c>
       <c r="R27" t="n">
-        <v>7332542</v>
+        <v>7332656</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3352,10 +3352,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120413493</v>
+        <v>120413474</v>
       </c>
       <c r="B28" t="n">
-        <v>77474</v>
+        <v>79652</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3364,25 +3364,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6487</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>625812</v>
+        <v>625828</v>
       </c>
       <c r="R28" t="n">
-        <v>7332838</v>
+        <v>7332701</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3454,7 +3454,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120413465</v>
+        <v>120413464</v>
       </c>
       <c r="B29" t="n">
         <v>79160</v>
@@ -3494,10 +3494,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>625854</v>
+        <v>625705</v>
       </c>
       <c r="R29" t="n">
-        <v>7332729</v>
+        <v>7332797</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3556,10 +3556,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120413480</v>
+        <v>120413471</v>
       </c>
       <c r="B30" t="n">
-        <v>78278</v>
+        <v>89650</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3572,21 +3572,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3596,10 +3596,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>625700</v>
+        <v>625815</v>
       </c>
       <c r="R30" t="n">
-        <v>7332827</v>
+        <v>7332543</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3658,10 +3658,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120413491</v>
+        <v>120413476</v>
       </c>
       <c r="B31" t="n">
-        <v>79658</v>
+        <v>92048</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3670,25 +3670,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6463</v>
+        <v>2079</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>625877</v>
+        <v>625812</v>
       </c>
       <c r="R31" t="n">
-        <v>7332740</v>
+        <v>7332547</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3760,10 +3760,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120413473</v>
+        <v>120413481</v>
       </c>
       <c r="B32" t="n">
-        <v>79652</v>
+        <v>78278</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3772,25 +3772,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>625875</v>
+        <v>625729</v>
       </c>
       <c r="R32" t="n">
-        <v>7332742</v>
+        <v>7332823</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3862,7 +3862,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120413481</v>
+        <v>120413480</v>
       </c>
       <c r="B33" t="n">
         <v>78278</v>
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>625729</v>
+        <v>625700</v>
       </c>
       <c r="R33" t="n">
-        <v>7332823</v>
+        <v>7332827</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4066,10 +4066,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120413467</v>
+        <v>120413486</v>
       </c>
       <c r="B35" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4082,21 +4082,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>625806</v>
+        <v>625706</v>
       </c>
       <c r="R35" t="n">
-        <v>7332496</v>
+        <v>7332827</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4168,10 +4168,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120413471</v>
+        <v>120413482</v>
       </c>
       <c r="B36" t="n">
-        <v>89650</v>
+        <v>78278</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4184,21 +4184,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>625815</v>
+        <v>625810</v>
       </c>
       <c r="R36" t="n">
-        <v>7332543</v>
+        <v>7332539</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4270,10 +4270,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120413479</v>
+        <v>120413492</v>
       </c>
       <c r="B37" t="n">
-        <v>78278</v>
+        <v>77474</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4286,21 +4286,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>625716</v>
+        <v>625705</v>
       </c>
       <c r="R37" t="n">
-        <v>7332805</v>
+        <v>7332799</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4372,10 +4372,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120413495</v>
+        <v>120413473</v>
       </c>
       <c r="B38" t="n">
-        <v>77926</v>
+        <v>79652</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4384,25 +4384,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6437</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>625813</v>
+        <v>625875</v>
       </c>
       <c r="R38" t="n">
-        <v>7332838</v>
+        <v>7332742</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4474,10 +4474,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120413474</v>
+        <v>120413487</v>
       </c>
       <c r="B39" t="n">
-        <v>79652</v>
+        <v>78187</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4486,25 +4486,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>625828</v>
+        <v>625806</v>
       </c>
       <c r="R39" t="n">
-        <v>7332701</v>
+        <v>7332495</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4576,10 +4576,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120413472</v>
+        <v>120413493</v>
       </c>
       <c r="B40" t="n">
-        <v>57473</v>
+        <v>77474</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4592,21 +4592,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>6487</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4619,7 +4619,7 @@
         <v>625812</v>
       </c>
       <c r="R40" t="n">
-        <v>7332656</v>
+        <v>7332838</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4678,10 +4678,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120413476</v>
+        <v>120413490</v>
       </c>
       <c r="B41" t="n">
-        <v>92048</v>
+        <v>79658</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4690,25 +4690,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2079</v>
+        <v>6463</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4718,10 +4718,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>625812</v>
+        <v>625853</v>
       </c>
       <c r="R41" t="n">
-        <v>7332547</v>
+        <v>7332733</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4780,10 +4780,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120413492</v>
+        <v>120413479</v>
       </c>
       <c r="B42" t="n">
-        <v>77474</v>
+        <v>78278</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4796,21 +4796,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4820,10 +4820,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>625705</v>
+        <v>625716</v>
       </c>
       <c r="R42" t="n">
-        <v>7332799</v>
+        <v>7332805</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4882,10 +4882,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120413477</v>
+        <v>120413465</v>
       </c>
       <c r="B43" t="n">
-        <v>79659</v>
+        <v>79160</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4894,25 +4894,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6464</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>625858</v>
+        <v>625854</v>
       </c>
       <c r="R43" t="n">
-        <v>7332733</v>
+        <v>7332729</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4984,10 +4984,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120413464</v>
+        <v>120413469</v>
       </c>
       <c r="B44" t="n">
-        <v>79160</v>
+        <v>79131</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5000,21 +5000,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5024,10 +5024,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>625705</v>
+        <v>625798</v>
       </c>
       <c r="R44" t="n">
-        <v>7332797</v>
+        <v>7332635</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 26089-2024 artfynd.xlsx
+++ b/artfynd/A 26089-2024 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120403757</v>
+        <v>120403754</v>
       </c>
       <c r="B4" t="n">
-        <v>78187</v>
+        <v>78278</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>625784</v>
+        <v>626005</v>
       </c>
       <c r="R4" t="n">
-        <v>7332766</v>
+        <v>7332708</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120403753</v>
+        <v>120403734</v>
       </c>
       <c r="B5" t="n">
-        <v>78278</v>
+        <v>90506</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,21 +1017,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>3242</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626012</v>
+        <v>626022</v>
       </c>
       <c r="R5" t="n">
-        <v>7332797</v>
+        <v>7332776</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120403751</v>
+        <v>120403737</v>
       </c>
       <c r="B6" t="n">
-        <v>78278</v>
+        <v>79160</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626087</v>
+        <v>625834</v>
       </c>
       <c r="R6" t="n">
-        <v>7332871</v>
+        <v>7332799</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120403759</v>
+        <v>120403757</v>
       </c>
       <c r="B7" t="n">
         <v>78187</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>625963</v>
+        <v>625784</v>
       </c>
       <c r="R7" t="n">
-        <v>7332633</v>
+        <v>7332766</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120403756</v>
+        <v>120403740</v>
       </c>
       <c r="B8" t="n">
-        <v>90730</v>
+        <v>89650</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,25 +1319,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1503</v>
+        <v>1962</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>625878</v>
+        <v>626010</v>
       </c>
       <c r="R8" t="n">
-        <v>7332849</v>
+        <v>7332796</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120403747</v>
+        <v>120403745</v>
       </c>
       <c r="B9" t="n">
-        <v>78279</v>
+        <v>89292</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,25 +1421,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626012</v>
+        <v>626005</v>
       </c>
       <c r="R9" t="n">
-        <v>7332797</v>
+        <v>7332687</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120403738</v>
+        <v>120403748</v>
       </c>
       <c r="B10" t="n">
-        <v>79160</v>
+        <v>78279</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626053</v>
+        <v>626004</v>
       </c>
       <c r="R10" t="n">
-        <v>7332836</v>
+        <v>7332686</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1613,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120403755</v>
+        <v>120403747</v>
       </c>
       <c r="B11" t="n">
-        <v>78278</v>
+        <v>78279</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626005</v>
+        <v>626012</v>
       </c>
       <c r="R11" t="n">
-        <v>7332686</v>
+        <v>7332797</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1715,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120403754</v>
+        <v>120403759</v>
       </c>
       <c r="B12" t="n">
-        <v>78278</v>
+        <v>78187</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,21 +1731,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626005</v>
+        <v>625963</v>
       </c>
       <c r="R12" t="n">
-        <v>7332708</v>
+        <v>7332633</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1817,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120403746</v>
+        <v>120403753</v>
       </c>
       <c r="B13" t="n">
-        <v>56532</v>
+        <v>78278</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1829,25 +1829,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>625839</v>
+        <v>626012</v>
       </c>
       <c r="R13" t="n">
-        <v>7332800</v>
+        <v>7332797</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1893,11 +1893,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1924,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120403748</v>
+        <v>120403751</v>
       </c>
       <c r="B14" t="n">
-        <v>78279</v>
+        <v>78278</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1940,21 +1935,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626004</v>
+        <v>626087</v>
       </c>
       <c r="R14" t="n">
-        <v>7332686</v>
+        <v>7332871</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2026,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120403745</v>
+        <v>120403756</v>
       </c>
       <c r="B15" t="n">
-        <v>89292</v>
+        <v>90730</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2042,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6286</v>
+        <v>1503</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2066,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626005</v>
+        <v>625878</v>
       </c>
       <c r="R15" t="n">
-        <v>7332687</v>
+        <v>7332849</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2128,7 +2123,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120403737</v>
+        <v>120403738</v>
       </c>
       <c r="B16" t="n">
         <v>79160</v>
@@ -2168,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>625834</v>
+        <v>626053</v>
       </c>
       <c r="R16" t="n">
-        <v>7332799</v>
+        <v>7332836</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2230,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120403742</v>
+        <v>120403755</v>
       </c>
       <c r="B17" t="n">
-        <v>89650</v>
+        <v>78278</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2246,21 +2241,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2270,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626003</v>
+        <v>626005</v>
       </c>
       <c r="R17" t="n">
-        <v>7332701</v>
+        <v>7332686</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2332,10 +2327,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120403734</v>
+        <v>120403746</v>
       </c>
       <c r="B18" t="n">
-        <v>90506</v>
+        <v>56532</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2344,25 +2339,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3242</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2372,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626022</v>
+        <v>625839</v>
       </c>
       <c r="R18" t="n">
-        <v>7332776</v>
+        <v>7332800</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2408,6 +2403,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2434,7 +2434,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120403740</v>
+        <v>120403742</v>
       </c>
       <c r="B19" t="n">
         <v>89650</v>
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626010</v>
+        <v>626003</v>
       </c>
       <c r="R19" t="n">
-        <v>7332796</v>
+        <v>7332701</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120413470</v>
+        <v>120413479</v>
       </c>
       <c r="B20" t="n">
-        <v>89650</v>
+        <v>78278</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2552,21 +2552,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>625715</v>
+        <v>625716</v>
       </c>
       <c r="R20" t="n">
-        <v>7332825</v>
+        <v>7332805</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2638,10 +2638,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120413475</v>
+        <v>120413493</v>
       </c>
       <c r="B21" t="n">
-        <v>91862</v>
+        <v>77474</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2650,25 +2650,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4365</v>
+        <v>6487</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>625802</v>
+        <v>625812</v>
       </c>
       <c r="R21" t="n">
-        <v>7332542</v>
+        <v>7332838</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2740,10 +2740,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120413467</v>
+        <v>120413473</v>
       </c>
       <c r="B22" t="n">
-        <v>79160</v>
+        <v>79652</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2752,25 +2752,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2780,10 +2780,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>625806</v>
+        <v>625875</v>
       </c>
       <c r="R22" t="n">
-        <v>7332496</v>
+        <v>7332742</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2842,10 +2842,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120413477</v>
+        <v>120413472</v>
       </c>
       <c r="B23" t="n">
-        <v>79659</v>
+        <v>57473</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2854,25 +2854,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2882,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>625858</v>
+        <v>625812</v>
       </c>
       <c r="R23" t="n">
-        <v>7332733</v>
+        <v>7332656</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2944,10 +2944,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120413485</v>
+        <v>120413474</v>
       </c>
       <c r="B24" t="n">
-        <v>78187</v>
+        <v>79652</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2956,25 +2956,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>625700</v>
+        <v>625828</v>
       </c>
       <c r="R24" t="n">
-        <v>7332818</v>
+        <v>7332701</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3046,10 +3046,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120413495</v>
+        <v>120413475</v>
       </c>
       <c r="B25" t="n">
-        <v>77926</v>
+        <v>91862</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3058,25 +3058,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6437</v>
+        <v>4365</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>625813</v>
+        <v>625802</v>
       </c>
       <c r="R25" t="n">
-        <v>7332838</v>
+        <v>7332542</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3148,10 +3148,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120413491</v>
+        <v>120413477</v>
       </c>
       <c r="B26" t="n">
-        <v>79658</v>
+        <v>79659</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3164,21 +3164,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>625877</v>
+        <v>625858</v>
       </c>
       <c r="R26" t="n">
-        <v>7332740</v>
+        <v>7332733</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3250,10 +3250,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120413472</v>
+        <v>120413488</v>
       </c>
       <c r="B27" t="n">
-        <v>57473</v>
+        <v>78187</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3266,21 +3266,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>625812</v>
+        <v>625806</v>
       </c>
       <c r="R27" t="n">
-        <v>7332656</v>
+        <v>7332495</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3352,10 +3352,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120413474</v>
+        <v>120413482</v>
       </c>
       <c r="B28" t="n">
-        <v>79652</v>
+        <v>78278</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3364,25 +3364,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>625828</v>
+        <v>625810</v>
       </c>
       <c r="R28" t="n">
-        <v>7332701</v>
+        <v>7332539</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3454,10 +3454,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120413464</v>
+        <v>120413495</v>
       </c>
       <c r="B29" t="n">
-        <v>79160</v>
+        <v>77926</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3470,21 +3470,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3494,10 +3494,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>625705</v>
+        <v>625813</v>
       </c>
       <c r="R29" t="n">
-        <v>7332797</v>
+        <v>7332838</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3556,10 +3556,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120413471</v>
+        <v>120413490</v>
       </c>
       <c r="B30" t="n">
-        <v>89650</v>
+        <v>79658</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3568,25 +3568,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1962</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3596,10 +3596,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>625815</v>
+        <v>625853</v>
       </c>
       <c r="R30" t="n">
-        <v>7332543</v>
+        <v>7332733</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3658,10 +3658,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120413476</v>
+        <v>120413486</v>
       </c>
       <c r="B31" t="n">
-        <v>92048</v>
+        <v>78187</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3674,21 +3674,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>625812</v>
+        <v>625706</v>
       </c>
       <c r="R31" t="n">
-        <v>7332547</v>
+        <v>7332827</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3760,7 +3760,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120413481</v>
+        <v>120413480</v>
       </c>
       <c r="B32" t="n">
         <v>78278</v>
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>625729</v>
+        <v>625700</v>
       </c>
       <c r="R32" t="n">
-        <v>7332823</v>
+        <v>7332827</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3862,10 +3862,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120413480</v>
+        <v>120413470</v>
       </c>
       <c r="B33" t="n">
-        <v>78278</v>
+        <v>89650</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3878,21 +3878,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>625700</v>
+        <v>625715</v>
       </c>
       <c r="R33" t="n">
-        <v>7332827</v>
+        <v>7332825</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3964,10 +3964,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120413494</v>
+        <v>120413465</v>
       </c>
       <c r="B34" t="n">
-        <v>77926</v>
+        <v>79160</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3980,21 +3980,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>625730</v>
+        <v>625854</v>
       </c>
       <c r="R34" t="n">
-        <v>7332818</v>
+        <v>7332729</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4066,7 +4066,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120413486</v>
+        <v>120413485</v>
       </c>
       <c r="B35" t="n">
         <v>78187</v>
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>625706</v>
+        <v>625700</v>
       </c>
       <c r="R35" t="n">
-        <v>7332827</v>
+        <v>7332818</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4168,10 +4168,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120413482</v>
+        <v>120413494</v>
       </c>
       <c r="B36" t="n">
-        <v>78278</v>
+        <v>77926</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4184,21 +4184,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>625810</v>
+        <v>625730</v>
       </c>
       <c r="R36" t="n">
-        <v>7332539</v>
+        <v>7332818</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4270,10 +4270,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120413492</v>
+        <v>120413471</v>
       </c>
       <c r="B37" t="n">
-        <v>77474</v>
+        <v>89650</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4286,21 +4286,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6487</v>
+        <v>1962</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>625705</v>
+        <v>625815</v>
       </c>
       <c r="R37" t="n">
-        <v>7332799</v>
+        <v>7332543</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4372,10 +4372,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120413473</v>
+        <v>120413491</v>
       </c>
       <c r="B38" t="n">
-        <v>79652</v>
+        <v>79658</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4388,21 +4388,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>625875</v>
+        <v>625877</v>
       </c>
       <c r="R38" t="n">
-        <v>7332742</v>
+        <v>7332740</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4474,10 +4474,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120413487</v>
+        <v>120413492</v>
       </c>
       <c r="B39" t="n">
-        <v>78187</v>
+        <v>77474</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4490,21 +4490,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>6487</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>625806</v>
+        <v>625705</v>
       </c>
       <c r="R39" t="n">
-        <v>7332495</v>
+        <v>7332799</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4576,10 +4576,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120413493</v>
+        <v>120413476</v>
       </c>
       <c r="B40" t="n">
-        <v>77474</v>
+        <v>92048</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4592,21 +4592,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6487</v>
+        <v>2079</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4619,7 +4619,7 @@
         <v>625812</v>
       </c>
       <c r="R40" t="n">
-        <v>7332838</v>
+        <v>7332547</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4678,10 +4678,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120413490</v>
+        <v>120413464</v>
       </c>
       <c r="B41" t="n">
-        <v>79658</v>
+        <v>79160</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4690,25 +4690,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6463</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4718,10 +4718,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>625853</v>
+        <v>625705</v>
       </c>
       <c r="R41" t="n">
-        <v>7332733</v>
+        <v>7332797</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4780,10 +4780,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120413479</v>
+        <v>120413469</v>
       </c>
       <c r="B42" t="n">
-        <v>78278</v>
+        <v>79131</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4796,21 +4796,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4820,10 +4820,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>625716</v>
+        <v>625798</v>
       </c>
       <c r="R42" t="n">
-        <v>7332805</v>
+        <v>7332635</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120413465</v>
+        <v>120413467</v>
       </c>
       <c r="B43" t="n">
         <v>79160</v>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>625854</v>
+        <v>625806</v>
       </c>
       <c r="R43" t="n">
-        <v>7332729</v>
+        <v>7332496</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4984,10 +4984,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120413469</v>
+        <v>120413481</v>
       </c>
       <c r="B44" t="n">
-        <v>79131</v>
+        <v>78278</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5000,21 +5000,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5024,10 +5024,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>625798</v>
+        <v>625729</v>
       </c>
       <c r="R44" t="n">
-        <v>7332635</v>
+        <v>7332823</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 26089-2024 artfynd.xlsx
+++ b/artfynd/A 26089-2024 artfynd.xlsx
@@ -4372,10 +4372,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120413491</v>
+        <v>120413476</v>
       </c>
       <c r="B38" t="n">
-        <v>79658</v>
+        <v>92048</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4384,25 +4384,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6463</v>
+        <v>2079</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>625877</v>
+        <v>625812</v>
       </c>
       <c r="R38" t="n">
-        <v>7332740</v>
+        <v>7332547</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4474,10 +4474,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120413492</v>
+        <v>120413491</v>
       </c>
       <c r="B39" t="n">
-        <v>77474</v>
+        <v>79658</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4486,25 +4486,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6487</v>
+        <v>6463</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>625705</v>
+        <v>625877</v>
       </c>
       <c r="R39" t="n">
-        <v>7332799</v>
+        <v>7332740</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4576,10 +4576,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120413476</v>
+        <v>120413492</v>
       </c>
       <c r="B40" t="n">
-        <v>92048</v>
+        <v>77474</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4592,21 +4592,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2079</v>
+        <v>6487</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4616,10 +4616,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>625812</v>
+        <v>625705</v>
       </c>
       <c r="R40" t="n">
-        <v>7332547</v>
+        <v>7332799</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>

--- a/artfynd/A 26089-2024 artfynd.xlsx
+++ b/artfynd/A 26089-2024 artfynd.xlsx
@@ -2228,7 +2228,7 @@
         <v>120403746</v>
       </c>
       <c r="B17" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 26089-2024 artfynd.xlsx
+++ b/artfynd/A 26089-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>123975</v>
       </c>
       <c r="B2" t="n">
-        <v>89632</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>625841.9629732999</v>
+        <v>625842</v>
       </c>
       <c r="R2" t="n">
-        <v>7332559.707593845</v>
+        <v>7332560</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2007-06-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2007-06-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,53 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>473616</v>
+        <v>120403757</v>
       </c>
       <c r="B3" t="n">
-        <v>89544</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gåglggamisvarre, Pi lm</t>
+          <t>Arjeplog, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>625931.8557473873</v>
+        <v>625784</v>
       </c>
       <c r="R3" t="n">
-        <v>7332550.701102231</v>
+        <v>7332766</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2007-06-14</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2007-06-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,27 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Teppo Rämä</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Teppo Rämä, * Naturskyddare</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120403747</v>
+        <v>120403759</v>
       </c>
       <c r="B4" t="n">
-        <v>78303</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626012</v>
+        <v>625963</v>
       </c>
       <c r="R4" t="n">
-        <v>7332797</v>
+        <v>7332633</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1001,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120403748</v>
+        <v>120413485</v>
       </c>
       <c r="B5" t="n">
-        <v>78303</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,37 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Arjeplog, Pi lm</t>
+          <t>NÖ Gålggåmisvárre, Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626004</v>
+        <v>625700</v>
       </c>
       <c r="R5" t="n">
-        <v>7332686</v>
+        <v>7332818</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,27 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120403740</v>
+        <v>120413486</v>
       </c>
       <c r="B6" t="n">
-        <v>89704</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,37 +1074,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Arjeplog, Pi lm</t>
+          <t>NÖ Gålggåmisvárre, Pi lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626010</v>
+        <v>625706</v>
       </c>
       <c r="R6" t="n">
-        <v>7332796</v>
+        <v>7332827</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,27 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120403751</v>
+        <v>120413487</v>
       </c>
       <c r="B7" t="n">
-        <v>78302</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,37 +1171,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Arjeplog, Pi lm</t>
+          <t>NÖ Gålggåmisvárre, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626087</v>
+        <v>625806</v>
       </c>
       <c r="R7" t="n">
-        <v>7332871</v>
+        <v>7332495</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,27 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120403756</v>
+        <v>473616</v>
       </c>
       <c r="B8" t="n">
-        <v>90798</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1343,17 +1288,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Arjeplog, Pi lm</t>
+          <t>Gåglggamisvarre, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>625878</v>
+        <v>625932</v>
       </c>
       <c r="R8" t="n">
-        <v>7332849</v>
+        <v>7332551</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1377,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>2007-06-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>2007-06-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,49 +1342,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Teppo Rämä</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Teppo Rämä, * Naturskyddare</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120403757</v>
+        <v>120403756</v>
       </c>
       <c r="B9" t="n">
-        <v>78211</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>625784</v>
+        <v>625878</v>
       </c>
       <c r="R9" t="n">
-        <v>7332766</v>
+        <v>7332849</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1511,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120403738</v>
+        <v>120403740</v>
       </c>
       <c r="B10" t="n">
-        <v>79184</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1527,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626053</v>
+        <v>626010</v>
       </c>
       <c r="R10" t="n">
-        <v>7332836</v>
+        <v>7332796</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1613,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120403754</v>
+        <v>120403742</v>
       </c>
       <c r="B11" t="n">
-        <v>78302</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1629,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626005</v>
+        <v>626003</v>
       </c>
       <c r="R11" t="n">
-        <v>7332708</v>
+        <v>7332701</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1715,15 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120403753</v>
+        <v>120403743</v>
       </c>
       <c r="B12" t="n">
-        <v>78302</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1731,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626012</v>
+        <v>625898</v>
       </c>
       <c r="R12" t="n">
-        <v>7332797</v>
+        <v>7332480</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1817,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120403734</v>
+        <v>120413470</v>
       </c>
       <c r="B13" t="n">
-        <v>90570</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1833,37 +1753,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3242</v>
+        <v>1962</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Arjeplog, Pi lm</t>
+          <t>NÖ Gålggåmisvárre, Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626022</v>
+        <v>625715</v>
       </c>
       <c r="R13" t="n">
-        <v>7332776</v>
+        <v>7332825</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1907,27 +1827,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120403759</v>
+        <v>120413471</v>
       </c>
       <c r="B14" t="n">
-        <v>78211</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,37 +1850,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Arjeplog, Pi lm</t>
+          <t>NÖ Gålggåmisvárre, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>625963</v>
+        <v>625815</v>
       </c>
       <c r="R14" t="n">
-        <v>7332633</v>
+        <v>7332543</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2009,27 +1924,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120403737</v>
+        <v>120413476</v>
       </c>
       <c r="B15" t="n">
-        <v>79184</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,37 +1947,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Arjeplog, Pi lm</t>
+          <t>NÖ Gålggåmisvárre, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>625834</v>
+        <v>625812</v>
       </c>
       <c r="R15" t="n">
-        <v>7332799</v>
+        <v>7332547</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2111,27 +2021,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120403755</v>
+        <v>120403734</v>
       </c>
       <c r="B16" t="n">
-        <v>78302</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2139,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>3242</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626005</v>
+        <v>626022</v>
       </c>
       <c r="R16" t="n">
-        <v>7332686</v>
+        <v>7332776</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2225,53 +2130,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120403746</v>
+        <v>120413475</v>
       </c>
       <c r="B17" t="n">
-        <v>56691</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>4365</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Arjeplog, Pi lm</t>
+          <t>NÖ Gålggåmisvárre, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>625839</v>
+        <v>625802</v>
       </c>
       <c r="R17" t="n">
-        <v>7332800</v>
+        <v>7332542</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2301,11 +2201,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2320,12 +2215,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2335,12 +2230,7 @@
         <v>120403745</v>
       </c>
       <c r="B18" t="n">
-        <v>89354</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90710</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2434,15 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120403742</v>
+        <v>120413494</v>
       </c>
       <c r="B19" t="n">
-        <v>89704</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2450,37 +2335,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1962</v>
+        <v>6437</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Arjeplog, Pi lm</t>
+          <t>NÖ Gålggåmisvárre, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626003</v>
+        <v>625730</v>
       </c>
       <c r="R19" t="n">
-        <v>7332701</v>
+        <v>7332818</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2524,27 +2409,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120413464</v>
+        <v>120413495</v>
       </c>
       <c r="B20" t="n">
-        <v>79184</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2552,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2576,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>625705</v>
+        <v>625813</v>
       </c>
       <c r="R20" t="n">
-        <v>7332797</v>
+        <v>7332838</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2638,53 +2518,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120413473</v>
+        <v>120403751</v>
       </c>
       <c r="B21" t="n">
-        <v>79676</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>NÖ Gålggåmisvárre, Pi lm</t>
+          <t>Arjeplog, Pi lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>625875</v>
+        <v>626087</v>
       </c>
       <c r="R21" t="n">
-        <v>7332742</v>
+        <v>7332871</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2728,27 +2603,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120413480</v>
+        <v>120403753</v>
       </c>
       <c r="B22" t="n">
-        <v>78302</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2776,17 +2646,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>NÖ Gålggåmisvárre, Pi lm</t>
+          <t>Arjeplog, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>625700</v>
+        <v>626012</v>
       </c>
       <c r="R22" t="n">
-        <v>7332827</v>
+        <v>7332797</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2830,27 +2700,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120413487</v>
+        <v>120403754</v>
       </c>
       <c r="B23" t="n">
-        <v>78211</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2858,37 +2723,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>NÖ Gålggåmisvárre, Pi lm</t>
+          <t>Arjeplog, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>625806</v>
+        <v>626005</v>
       </c>
       <c r="R23" t="n">
-        <v>7332495</v>
+        <v>7332708</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2932,65 +2797,60 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120413475</v>
+        <v>120403755</v>
       </c>
       <c r="B24" t="n">
-        <v>91923</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4365</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>NÖ Gålggåmisvárre, Pi lm</t>
+          <t>Arjeplog, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>625802</v>
+        <v>626005</v>
       </c>
       <c r="R24" t="n">
-        <v>7332542</v>
+        <v>7332686</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3034,27 +2894,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120413486</v>
+        <v>120413479</v>
       </c>
       <c r="B25" t="n">
-        <v>78211</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3062,21 +2917,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3086,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>625706</v>
+        <v>625716</v>
       </c>
       <c r="R25" t="n">
-        <v>7332827</v>
+        <v>7332805</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3148,37 +3003,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120413491</v>
+        <v>120413480</v>
       </c>
       <c r="B26" t="n">
-        <v>79682</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3188,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>625877</v>
+        <v>625700</v>
       </c>
       <c r="R26" t="n">
-        <v>7332740</v>
+        <v>7332827</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3250,15 +3100,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120413467</v>
+        <v>120413481</v>
       </c>
       <c r="B27" t="n">
-        <v>79184</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3266,21 +3111,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3290,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>625806</v>
+        <v>625729</v>
       </c>
       <c r="R27" t="n">
-        <v>7332496</v>
+        <v>7332823</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3355,12 +3200,7 @@
         <v>120413482</v>
       </c>
       <c r="B28" t="n">
-        <v>78302</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3454,15 +3294,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120413465</v>
+        <v>120403737</v>
       </c>
       <c r="B29" t="n">
-        <v>79184</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3490,17 +3325,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>NÖ Gålggåmisvárre, Pi lm</t>
+          <t>Arjeplog, Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>625854</v>
+        <v>625834</v>
       </c>
       <c r="R29" t="n">
-        <v>7332729</v>
+        <v>7332799</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3544,27 +3379,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120413479</v>
+        <v>120403738</v>
       </c>
       <c r="B30" t="n">
-        <v>78302</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3572,37 +3402,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>NÖ Gålggåmisvárre, Pi lm</t>
+          <t>Arjeplog, Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>625716</v>
+        <v>626053</v>
       </c>
       <c r="R30" t="n">
-        <v>7332805</v>
+        <v>7332836</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3646,27 +3476,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120413495</v>
+        <v>120413464</v>
       </c>
       <c r="B31" t="n">
-        <v>77950</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3674,21 +3499,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3698,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>625813</v>
+        <v>625705</v>
       </c>
       <c r="R31" t="n">
-        <v>7332838</v>
+        <v>7332797</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3760,15 +3585,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120413485</v>
+        <v>120413465</v>
       </c>
       <c r="B32" t="n">
-        <v>78211</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3776,21 +3596,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3800,10 +3620,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>625700</v>
+        <v>625854</v>
       </c>
       <c r="R32" t="n">
-        <v>7332818</v>
+        <v>7332729</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3862,15 +3682,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120413493</v>
+        <v>120413467</v>
       </c>
       <c r="B33" t="n">
-        <v>77498</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3878,21 +3693,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3902,10 +3717,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>625812</v>
+        <v>625806</v>
       </c>
       <c r="R33" t="n">
-        <v>7332838</v>
+        <v>7332496</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3964,15 +3779,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120413477</v>
+        <v>120413473</v>
       </c>
       <c r="B34" t="n">
-        <v>79683</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3980,21 +3790,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4004,10 +3814,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>625858</v>
+        <v>625875</v>
       </c>
       <c r="R34" t="n">
-        <v>7332733</v>
+        <v>7332742</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4066,37 +3876,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120413472</v>
+        <v>120413474</v>
       </c>
       <c r="B35" t="n">
-        <v>57488</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4106,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>625812</v>
+        <v>625828</v>
       </c>
       <c r="R35" t="n">
-        <v>7332656</v>
+        <v>7332701</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4168,37 +3973,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120413492</v>
+        <v>120413490</v>
       </c>
       <c r="B36" t="n">
-        <v>77498</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6487</v>
+        <v>6463</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4208,10 +4008,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>625705</v>
+        <v>625853</v>
       </c>
       <c r="R36" t="n">
-        <v>7332799</v>
+        <v>7332733</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4270,15 +4070,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120413474</v>
+        <v>120413491</v>
       </c>
       <c r="B37" t="n">
-        <v>79676</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4286,21 +4081,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4310,10 +4105,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>625828</v>
+        <v>625877</v>
       </c>
       <c r="R37" t="n">
-        <v>7332701</v>
+        <v>7332740</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4372,37 +4167,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120413469</v>
+        <v>120413477</v>
       </c>
       <c r="B38" t="n">
-        <v>79155</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>6464</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4412,10 +4202,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>625798</v>
+        <v>625858</v>
       </c>
       <c r="R38" t="n">
-        <v>7332635</v>
+        <v>7332733</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4474,15 +4264,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120413471</v>
+        <v>120413492</v>
       </c>
       <c r="B39" t="n">
-        <v>89704</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4490,21 +4275,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1962</v>
+        <v>6487</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4514,10 +4299,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>625815</v>
+        <v>625705</v>
       </c>
       <c r="R39" t="n">
-        <v>7332543</v>
+        <v>7332799</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4576,15 +4361,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120413481</v>
+        <v>120413493</v>
       </c>
       <c r="B40" t="n">
-        <v>78302</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4592,21 +4372,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4616,10 +4396,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>625729</v>
+        <v>625812</v>
       </c>
       <c r="R40" t="n">
-        <v>7332823</v>
+        <v>7332838</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4678,53 +4458,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120413476</v>
+        <v>120403746</v>
       </c>
       <c r="B41" t="n">
-        <v>92116</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2079</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>NÖ Gålggåmisvárre, Pi lm</t>
+          <t>Arjeplog, Pi lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>625812</v>
+        <v>625839</v>
       </c>
       <c r="R41" t="n">
-        <v>7332547</v>
+        <v>7332800</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4754,6 +4529,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4768,27 +4548,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120413470</v>
+        <v>120413472</v>
       </c>
       <c r="B42" t="n">
-        <v>89704</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4796,21 +4571,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1962</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4820,10 +4595,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>625715</v>
+        <v>625812</v>
       </c>
       <c r="R42" t="n">
-        <v>7332825</v>
+        <v>7332656</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4882,53 +4657,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120413490</v>
+        <v>120403747</v>
       </c>
       <c r="B43" t="n">
-        <v>79682</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>NÖ Gålggåmisvárre, Pi lm</t>
+          <t>Arjeplog, Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>625853</v>
+        <v>626012</v>
       </c>
       <c r="R43" t="n">
-        <v>7332733</v>
+        <v>7332797</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4972,27 +4742,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120413494</v>
+        <v>120403748</v>
       </c>
       <c r="B44" t="n">
-        <v>77950</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5000,37 +4765,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>NÖ Gålggåmisvárre, Pi lm</t>
+          <t>Arjeplog, Pi lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>625730</v>
+        <v>626004</v>
       </c>
       <c r="R44" t="n">
-        <v>7332818</v>
+        <v>7332686</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5074,15 +4839,112 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>120413469</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>NÖ Gålggåmisvárre, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>625798</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7332635</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
           <t>Linda Nordström</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
+      <c r="AX45" t="inlineStr">
         <is>
           <t>Linda Nordström</t>
         </is>
       </c>
-      <c r="AY44" t="inlineStr"/>
+      <c r="AY45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26089-2024 artfynd.xlsx
+++ b/artfynd/A 26089-2024 artfynd.xlsx
@@ -17186,6 +17186,9 @@
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Gålggåmisvárre, Pi lm</t>
@@ -17261,7 +17264,11 @@
           <t>Ann Normark</t>
         </is>
       </c>
-      <c r="AY152" t="inlineStr"/>
+      <c r="AY152" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">

--- a/artfynd/A 26089-2024 artfynd.xlsx
+++ b/artfynd/A 26089-2024 artfynd.xlsx
@@ -8891,6 +8891,9 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Gålggåmisvárre, Pi lm</t>
@@ -8947,7 +8950,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Fruktkroppar från i fjol</t>
+          <t>Fruktkroppar från i fjol. Torr tallskog, kuperad sandig grusig morän.</t>
         </is>
       </c>
       <c r="AD76" t="b">

--- a/artfynd/A 26089-2024 artfynd.xlsx
+++ b/artfynd/A 26089-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY297"/>
+  <dimension ref="A1:AZ297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123975</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295377</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1019,6 +1034,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294352</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413487</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1261,6 +1286,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294350</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1368,6 +1398,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294354</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1479,6 +1514,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294783</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1590,6 +1630,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294850</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1701,6 +1746,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294854</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1812,6 +1862,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295381</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1923,6 +1978,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295383</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2034,6 +2094,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300485</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2150,6 +2215,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300572</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2261,6 +2331,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301725</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2372,6 +2447,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301737</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2483,6 +2563,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301777</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2594,6 +2679,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301793</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2705,6 +2795,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294795</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2816,6 +2911,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301800</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2913,6 +3013,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/473616</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3024,6 +3129,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300576</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3121,6 +3231,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403743</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3218,6 +3333,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413471</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3329,6 +3449,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294851</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3426,6 +3551,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413476</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3537,6 +3667,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301730</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3644,6 +3779,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294359</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3755,6 +3895,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294852</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3852,6 +3997,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413475</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3994,6 +4144,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294351</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4105,6 +4260,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301732</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4216,6 +4376,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301797</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4323,6 +4488,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294358</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4420,6 +4590,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413482</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4531,6 +4706,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295380</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4628,6 +4808,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413467</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4739,6 +4924,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294782</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4850,6 +5040,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294787</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4961,6 +5156,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294788</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5072,6 +5272,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294790</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5183,6 +5388,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294794</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5294,6 +5504,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294836</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5405,6 +5620,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294847</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5516,6 +5736,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294849</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5627,6 +5852,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295388</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5738,6 +5968,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301733</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5847,6 +6082,11 @@
       <c r="AY48" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301780</t>
         </is>
       </c>
     </row>
@@ -5969,6 +6209,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294378</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6085,6 +6330,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294789</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6196,6 +6446,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298432</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6312,6 +6567,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301804</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6428,6 +6688,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301803</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6535,6 +6800,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294357</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6646,6 +6916,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294781</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6755,6 +7030,11 @@
       <c r="AY56" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294843</t>
         </is>
       </c>
     </row>
@@ -6873,6 +7153,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295389</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6984,6 +7269,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301728</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7095,6 +7385,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301791</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7206,6 +7501,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295379</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7317,6 +7617,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301778</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7428,6 +7733,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301796</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7535,6 +7845,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294355</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7646,6 +7961,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295378</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7757,6 +8077,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295386</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7868,6 +8193,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295387</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7979,6 +8309,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300574</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8090,6 +8425,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300575</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8201,6 +8541,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301794</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8308,6 +8653,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294356</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8419,6 +8769,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294853</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8530,6 +8885,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295384</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8642,6 +9002,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295385</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8753,6 +9118,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301727</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8862,6 +9232,11 @@
       <c r="AY75" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301735</t>
         </is>
       </c>
     </row>
@@ -8979,6 +9354,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295442</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9086,6 +9466,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301801</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9197,6 +9582,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300502</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9294,6 +9684,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403757</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9391,6 +9786,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403759</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9488,6 +9888,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413485</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9585,6 +9990,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413486</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9692,6 +10102,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294364</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9799,6 +10214,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294374</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9910,6 +10330,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294791</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10021,6 +10446,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294800</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10132,6 +10562,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294823</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10243,6 +10678,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294824</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10354,6 +10794,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294837</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10465,6 +10910,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298434</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10576,6 +11026,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298439</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10687,6 +11142,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298457</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10798,6 +11258,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298458</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10909,6 +11374,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300494</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11020,6 +11490,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300500</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11131,6 +11606,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300504</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11247,6 +11727,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300508</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11363,6 +11848,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300511</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11474,6 +11964,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300526</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11585,6 +12080,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300531</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11701,6 +12201,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300534</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11812,6 +12317,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300537</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11923,6 +12433,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300541</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12034,6 +12549,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300552</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12145,6 +12665,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300555</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12256,6 +12781,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300560</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12367,6 +12897,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300561</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12483,6 +13018,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300562</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12594,6 +13134,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300568</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12705,6 +13250,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300569</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12816,6 +13366,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301768</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12927,6 +13482,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294811</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13038,6 +13598,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300523</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13150,6 +13715,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301784</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13261,6 +13831,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300510</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13358,6 +13933,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403756</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13485,6 +14065,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294361</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13596,6 +14181,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295390</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13703,6 +14293,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298393</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13810,6 +14405,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298394</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13917,6 +14517,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298401</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14028,6 +14633,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298436</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14139,6 +14749,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298437</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14250,6 +14865,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300514</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14361,6 +14981,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300540</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14472,6 +15097,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300566</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14569,6 +15199,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403740</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14666,6 +15301,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403742</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14763,6 +15403,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413470</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14870,6 +15515,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294365</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14981,6 +15631,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300496</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15092,6 +15747,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300513</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15203,6 +15863,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300516</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15314,6 +15979,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300519</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15411,6 +16081,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403734</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15522,6 +16197,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300542</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15638,6 +16318,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294829</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15745,6 +16430,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294363</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15856,6 +16546,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294839</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15967,6 +16662,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298447</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16083,6 +16783,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301769</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16199,6 +16904,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301776</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16315,6 +17025,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301781</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16426,6 +17141,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301740</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16537,6 +17257,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300495</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16634,6 +17359,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403745</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16745,6 +17475,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300520</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16842,6 +17577,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413494</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16939,6 +17679,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413495</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17050,6 +17795,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294797</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17157,6 +17907,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298397</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17272,6 +18027,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298398</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17383,6 +18143,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298433</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17494,6 +18259,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300487</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17605,6 +18375,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300509</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17716,6 +18491,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300525</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -17827,6 +18607,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300529</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17924,6 +18709,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403751</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18021,6 +18811,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403753</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18118,6 +18913,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403754</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18215,6 +19015,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403755</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18312,6 +19117,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413479</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18409,6 +19219,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413480</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18506,6 +19321,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413481</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -18617,6 +19437,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294821</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -18728,6 +19553,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298443</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -18839,6 +19669,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300507</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18950,6 +19785,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300515</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -19061,6 +19901,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300521</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -19172,6 +20017,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301762</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -19269,6 +20119,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403737</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -19366,6 +20221,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403738</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -19463,6 +20323,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413464</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -19560,6 +20425,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413465</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -19667,6 +20537,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294373</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -19774,6 +20649,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294375</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -19885,6 +20765,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294784</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -19996,6 +20881,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294799</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -20107,6 +20997,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294813</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -20218,6 +21113,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294818</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -20329,6 +21229,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294820</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -20440,6 +21345,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294827</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -20551,6 +21461,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294830</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -20662,6 +21577,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294834</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -20773,6 +21693,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294840</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -20880,6 +21805,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298391</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -20991,6 +21921,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298435</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -21102,6 +22037,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298459</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -21213,6 +22153,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300492</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -21324,6 +22269,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300498</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -21435,6 +22385,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300503</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -21546,6 +22501,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300517</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -21657,6 +22617,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300530</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -21768,6 +22733,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300532</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -21879,6 +22849,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300536</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -21990,6 +22965,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300547</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -22101,6 +23081,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300548</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -22212,6 +23197,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300551</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -22323,6 +23313,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300565</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -22434,6 +23429,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301743</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -22545,6 +23545,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301764</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -22656,6 +23661,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301774</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -22767,6 +23777,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301783</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -22878,6 +23893,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301786</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -22989,6 +24009,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301788</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -23100,6 +24125,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300544</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -23211,6 +24241,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300545</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -23322,6 +24357,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294793</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -23419,6 +24459,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413473</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -23516,6 +24561,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413474</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -23627,6 +24677,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294807</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -23738,6 +24793,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294815</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -23849,6 +24909,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301748</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -23946,6 +25011,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413490</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -24043,6 +25113,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413491</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -24154,6 +25229,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294805</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -24265,6 +25345,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301749</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -24376,6 +25461,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301754</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -24473,6 +25563,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413477</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -24584,6 +25679,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301751</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -24681,6 +25781,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413492</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -24778,6 +25883,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413493</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -24889,6 +25999,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300527</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -25000,6 +26115,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294809</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -25116,6 +26236,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300506</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -25232,6 +26357,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300543</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -25334,6 +26464,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403746</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -25451,6 +26586,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294360</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -25567,6 +26707,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294810</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -25691,6 +26836,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298406</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -25802,6 +26952,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298438</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -25918,6 +27073,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298440</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -26034,6 +27194,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298445</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -26150,6 +27315,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300490</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -26266,6 +27436,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300553</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -26382,6 +27557,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300563</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -26498,6 +27678,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300567</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -26595,6 +27780,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413472</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -26710,6 +27900,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294832</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -26821,6 +28016,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301755</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -26937,6 +28137,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294377</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -27057,6 +28262,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300538</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -27173,6 +28383,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301738</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -27284,6 +28499,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300501</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -27395,6 +28615,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301756</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -27506,6 +28731,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294816</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -27617,6 +28847,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301744</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -27728,6 +28963,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294825</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -27839,6 +29079,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294841</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -27950,6 +29195,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300497</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -28061,6 +29311,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301741</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -28172,6 +29427,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301757</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -28283,6 +29543,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301766</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -28394,6 +29659,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301770</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -28505,6 +29775,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301790</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -28616,6 +29891,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298442</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -28727,6 +30007,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301747</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -28838,6 +30123,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301759</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -28949,6 +30239,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295146</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -29046,6 +30341,11 @@
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403747</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -29143,6 +30443,11 @@
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403748</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -29254,6 +30559,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298444</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -29365,6 +30675,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298446</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -29476,6 +30791,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300488</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -29587,6 +30907,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300493</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -29698,6 +31023,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300550</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -29809,6 +31139,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301752</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -29906,6 +31241,11 @@
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120413469</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -30017,6 +31357,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294785</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -30128,6 +31473,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294801</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -30239,6 +31589,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294812</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -30350,6 +31705,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294826</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -30461,6 +31821,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294833</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -30568,6 +31933,11 @@
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298403</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -30675,6 +32045,11 @@
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298407</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -30786,6 +32161,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300489</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -30897,6 +32277,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300491</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -31008,6 +32393,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300524</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -31119,6 +32509,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300528</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -31230,6 +32625,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300533</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -31341,6 +32741,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300539</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -31452,6 +32857,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300546</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -31563,6 +32973,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300549</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -31674,6 +33089,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300554</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -31785,6 +33205,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300557</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -31896,6 +33321,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300564</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -32007,6 +33437,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301787</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -32114,6 +33549,11 @@
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135291042</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -32221,6 +33661,11 @@
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294362</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -32328,6 +33773,11 @@
         </is>
       </c>
       <c r="AY290" t="inlineStr"/>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294376</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -32439,6 +33889,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294796</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -32550,6 +34005,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294828</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -32661,6 +34121,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294831</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -32772,6 +34237,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294835</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -32888,6 +34358,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300505</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -32999,6 +34474,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301765</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -33110,8 +34590,311 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ297" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301773</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ297" r:id="rId296"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 26089-2024 artfynd.xlsx
+++ b/artfynd/A 26089-2024 artfynd.xlsx
@@ -6076,7 +6076,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Pia Edfors, Petra Wikström</t>
+          <t>Petra Wikström, Pia Edfors</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -13707,7 +13707,7 @@
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Pia Edfors, Petra Wikström</t>
+          <t>Petra Wikström, Pia Edfors</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -17017,7 +17017,7 @@
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Pia Edfors, Petra Wikström</t>
+          <t>Petra Wikström, Pia Edfors</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
@@ -23769,7 +23769,7 @@
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Pia Edfors, Petra Wikström</t>
+          <t>Petra Wikström, Pia Edfors</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">

--- a/artfynd/A 26089-2024 artfynd.xlsx
+++ b/artfynd/A 26089-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135295377</v>
       </c>
       <c r="B3" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>135294352</v>
       </c>
       <c r="B4" t="n">
-        <v>92369</v>
+        <v>92411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135294350</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>135294354</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>135294783</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>135294850</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>135294854</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>135295381</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>135295383</v>
       </c>
       <c r="B12" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>135300485</v>
       </c>
       <c r="B13" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>135300572</v>
       </c>
       <c r="B14" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>135301725</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>135301737</v>
       </c>
       <c r="B16" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>135301777</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>135301793</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>135294795</v>
       </c>
       <c r="B19" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>135301800</v>
       </c>
       <c r="B20" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>135300576</v>
       </c>
       <c r="B22" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>135294851</v>
       </c>
       <c r="B25" t="n">
-        <v>90997</v>
+        <v>91039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>135301730</v>
       </c>
       <c r="B27" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>135294359</v>
       </c>
       <c r="B28" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>135294852</v>
       </c>
       <c r="B29" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>135294351</v>
       </c>
       <c r="B31" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135301732</v>
       </c>
       <c r="B32" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>135301797</v>
       </c>
       <c r="B33" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>135294358</v>
       </c>
       <c r="B34" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>135295380</v>
       </c>
       <c r="B36" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         <v>135294782</v>
       </c>
       <c r="B38" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>135294787</v>
       </c>
       <c r="B39" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>135294788</v>
       </c>
       <c r="B40" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>135294790</v>
       </c>
       <c r="B41" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>135294794</v>
       </c>
       <c r="B42" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>135294836</v>
       </c>
       <c r="B43" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>135294847</v>
       </c>
       <c r="B44" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>135294849</v>
       </c>
       <c r="B45" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>135295388</v>
       </c>
       <c r="B46" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>135301733</v>
       </c>
       <c r="B47" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>135301780</v>
       </c>
       <c r="B48" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Petra Wikström, Pia Edfors</t>
+          <t>Pia Edfors, Petra Wikström</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -6095,7 +6095,7 @@
         <v>135294378</v>
       </c>
       <c r="B49" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>135294789</v>
       </c>
       <c r="B50" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>135298432</v>
       </c>
       <c r="B51" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         <v>135301804</v>
       </c>
       <c r="B52" t="n">
-        <v>57165</v>
+        <v>57170</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>135301803</v>
       </c>
       <c r="B53" t="n">
-        <v>8449</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>135294357</v>
       </c>
       <c r="B54" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>135294781</v>
       </c>
       <c r="B55" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         <v>135294843</v>
       </c>
       <c r="B56" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>135295389</v>
       </c>
       <c r="B57" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>135301728</v>
       </c>
       <c r="B58" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>135301791</v>
       </c>
       <c r="B59" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>135295379</v>
       </c>
       <c r="B60" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>135301778</v>
       </c>
       <c r="B61" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7628,7 +7628,7 @@
         <v>135301796</v>
       </c>
       <c r="B62" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>135294355</v>
       </c>
       <c r="B63" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>135295378</v>
       </c>
       <c r="B64" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>135295386</v>
       </c>
       <c r="B65" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>135295387</v>
       </c>
       <c r="B66" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>135300574</v>
       </c>
       <c r="B67" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>135300575</v>
       </c>
       <c r="B68" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>135301794</v>
       </c>
       <c r="B69" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         <v>135294356</v>
       </c>
       <c r="B70" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>135294853</v>
       </c>
       <c r="B71" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>135295384</v>
       </c>
       <c r="B72" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>135295385</v>
       </c>
       <c r="B73" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>135301727</v>
       </c>
       <c r="B74" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>135301735</v>
       </c>
       <c r="B75" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>135295442</v>
       </c>
       <c r="B76" t="n">
-        <v>93292</v>
+        <v>93334</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         <v>135301801</v>
       </c>
       <c r="B77" t="n">
-        <v>93292</v>
+        <v>93334</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>135300502</v>
       </c>
       <c r="B78" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>135294364</v>
       </c>
       <c r="B83" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>135294374</v>
       </c>
       <c r="B84" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>135294791</v>
       </c>
       <c r="B85" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         <v>135294800</v>
       </c>
       <c r="B86" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10457,7 +10457,7 @@
         <v>135294823</v>
       </c>
       <c r="B87" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>135294824</v>
       </c>
       <c r="B88" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>135294837</v>
       </c>
       <c r="B89" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>135298434</v>
       </c>
       <c r="B90" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>135298439</v>
       </c>
       <c r="B91" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>135298457</v>
       </c>
       <c r="B92" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>135298458</v>
       </c>
       <c r="B93" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>135300494</v>
       </c>
       <c r="B94" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         <v>135300500</v>
       </c>
       <c r="B95" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>135300504</v>
       </c>
       <c r="B96" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>135300508</v>
       </c>
       <c r="B97" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11738,7 +11738,7 @@
         <v>135300511</v>
       </c>
       <c r="B98" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>135300526</v>
       </c>
       <c r="B99" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
         <v>135300531</v>
       </c>
       <c r="B100" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12091,7 +12091,7 @@
         <v>135300534</v>
       </c>
       <c r="B101" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>135300537</v>
       </c>
       <c r="B102" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12328,7 +12328,7 @@
         <v>135300541</v>
       </c>
       <c r="B103" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>135300552</v>
       </c>
       <c r="B104" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>135300555</v>
       </c>
       <c r="B105" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>135300560</v>
       </c>
       <c r="B106" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12792,7 +12792,7 @@
         <v>135300561</v>
       </c>
       <c r="B107" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>135300562</v>
       </c>
       <c r="B108" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>135300568</v>
       </c>
       <c r="B109" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>135300569</v>
       </c>
       <c r="B110" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>135301768</v>
       </c>
       <c r="B111" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         <v>135294811</v>
       </c>
       <c r="B112" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13493,7 +13493,7 @@
         <v>135300523</v>
       </c>
       <c r="B113" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>135301784</v>
       </c>
       <c r="B114" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13707,7 +13707,7 @@
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Petra Wikström, Pia Edfors</t>
+          <t>Pia Edfors, Petra Wikström</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -13726,7 +13726,7 @@
         <v>135300510</v>
       </c>
       <c r="B115" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>135294361</v>
       </c>
       <c r="B117" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>135295390</v>
       </c>
       <c r="B118" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>135298393</v>
       </c>
       <c r="B119" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>135298394</v>
       </c>
       <c r="B120" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>135298401</v>
       </c>
       <c r="B121" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>135298436</v>
       </c>
       <c r="B122" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14644,7 +14644,7 @@
         <v>135298437</v>
       </c>
       <c r="B123" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>135300514</v>
       </c>
       <c r="B124" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14876,7 +14876,7 @@
         <v>135300540</v>
       </c>
       <c r="B125" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>135300566</v>
       </c>
       <c r="B126" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>135294365</v>
       </c>
       <c r="B130" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>135300496</v>
       </c>
       <c r="B131" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>135300513</v>
       </c>
       <c r="B132" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15758,7 +15758,7 @@
         <v>135300516</v>
       </c>
       <c r="B133" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>135300519</v>
       </c>
       <c r="B134" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         <v>135300542</v>
       </c>
       <c r="B136" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>135294829</v>
       </c>
       <c r="B137" t="n">
-        <v>93265</v>
+        <v>93307</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>135294363</v>
       </c>
       <c r="B138" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16441,7 +16441,7 @@
         <v>135294839</v>
       </c>
       <c r="B139" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16557,7 +16557,7 @@
         <v>135298447</v>
       </c>
       <c r="B140" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>135301769</v>
       </c>
       <c r="B141" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16794,7 +16794,7 @@
         <v>135301776</v>
       </c>
       <c r="B142" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>135301781</v>
       </c>
       <c r="B143" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17017,7 +17017,7 @@
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Petra Wikström, Pia Edfors</t>
+          <t>Pia Edfors, Petra Wikström</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
@@ -17036,7 +17036,7 @@
         <v>135301740</v>
       </c>
       <c r="B144" t="n">
-        <v>93275</v>
+        <v>93317</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>135300495</v>
       </c>
       <c r="B145" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17370,7 +17370,7 @@
         <v>135300520</v>
       </c>
       <c r="B147" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17690,7 +17690,7 @@
         <v>135294797</v>
       </c>
       <c r="B150" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17806,7 +17806,7 @@
         <v>135298397</v>
       </c>
       <c r="B151" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
         <v>135298398</v>
       </c>
       <c r="B152" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18038,7 +18038,7 @@
         <v>135298433</v>
       </c>
       <c r="B153" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>135300487</v>
       </c>
       <c r="B154" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         <v>135300509</v>
       </c>
       <c r="B155" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>135300525</v>
       </c>
       <c r="B156" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18502,7 +18502,7 @@
         <v>135300529</v>
       </c>
       <c r="B157" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>135294821</v>
       </c>
       <c r="B165" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19448,7 +19448,7 @@
         <v>135298443</v>
       </c>
       <c r="B166" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19564,7 +19564,7 @@
         <v>135300507</v>
       </c>
       <c r="B167" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19680,7 +19680,7 @@
         <v>135300515</v>
       </c>
       <c r="B168" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>135300521</v>
       </c>
       <c r="B169" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>135301762</v>
       </c>
       <c r="B170" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20436,7 +20436,7 @@
         <v>135294373</v>
       </c>
       <c r="B175" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20548,7 +20548,7 @@
         <v>135294375</v>
       </c>
       <c r="B176" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         <v>135294784</v>
       </c>
       <c r="B177" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>135294799</v>
       </c>
       <c r="B178" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20892,7 +20892,7 @@
         <v>135294813</v>
       </c>
       <c r="B179" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>135294818</v>
       </c>
       <c r="B180" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21124,7 +21124,7 @@
         <v>135294820</v>
       </c>
       <c r="B181" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21240,7 +21240,7 @@
         <v>135294827</v>
       </c>
       <c r="B182" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21356,7 +21356,7 @@
         <v>135294830</v>
       </c>
       <c r="B183" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21472,7 +21472,7 @@
         <v>135294834</v>
       </c>
       <c r="B184" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21588,7 +21588,7 @@
         <v>135294840</v>
       </c>
       <c r="B185" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21704,7 +21704,7 @@
         <v>135298391</v>
       </c>
       <c r="B186" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>135298435</v>
       </c>
       <c r="B187" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21932,7 +21932,7 @@
         <v>135298459</v>
       </c>
       <c r="B188" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22048,7 +22048,7 @@
         <v>135300492</v>
       </c>
       <c r="B189" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>135300498</v>
       </c>
       <c r="B190" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>135300503</v>
       </c>
       <c r="B191" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22396,7 +22396,7 @@
         <v>135300517</v>
       </c>
       <c r="B192" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>135300530</v>
       </c>
       <c r="B193" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -22628,7 +22628,7 @@
         <v>135300532</v>
       </c>
       <c r="B194" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>135300536</v>
       </c>
       <c r="B195" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -22860,7 +22860,7 @@
         <v>135300547</v>
       </c>
       <c r="B196" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22976,7 +22976,7 @@
         <v>135300548</v>
       </c>
       <c r="B197" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23092,7 +23092,7 @@
         <v>135300551</v>
       </c>
       <c r="B198" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23208,7 +23208,7 @@
         <v>135300565</v>
       </c>
       <c r="B199" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>135301743</v>
       </c>
       <c r="B200" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23440,7 +23440,7 @@
         <v>135301764</v>
       </c>
       <c r="B201" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>135301774</v>
       </c>
       <c r="B202" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -23672,7 +23672,7 @@
         <v>135301783</v>
       </c>
       <c r="B203" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -23769,7 +23769,7 @@
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Petra Wikström, Pia Edfors</t>
+          <t>Pia Edfors, Petra Wikström</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
@@ -23788,7 +23788,7 @@
         <v>135301786</v>
       </c>
       <c r="B204" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23904,7 +23904,7 @@
         <v>135301788</v>
       </c>
       <c r="B205" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24020,7 +24020,7 @@
         <v>135300544</v>
       </c>
       <c r="B206" t="n">
-        <v>80382</v>
+        <v>80420</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
         <v>135300545</v>
       </c>
       <c r="B207" t="n">
-        <v>80382</v>
+        <v>80420</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>135294793</v>
       </c>
       <c r="B208" t="n">
-        <v>80492</v>
+        <v>80530</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>135294807</v>
       </c>
       <c r="B211" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>135294815</v>
       </c>
       <c r="B212" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>135301748</v>
       </c>
       <c r="B213" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>135294805</v>
       </c>
       <c r="B216" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25240,7 +25240,7 @@
         <v>135301749</v>
       </c>
       <c r="B217" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25356,7 +25356,7 @@
         <v>135301754</v>
       </c>
       <c r="B218" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25574,7 +25574,7 @@
         <v>135301751</v>
       </c>
       <c r="B220" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -25894,7 +25894,7 @@
         <v>135300527</v>
       </c>
       <c r="B223" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>135294809</v>
       </c>
       <c r="B224" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26126,7 +26126,7 @@
         <v>135300506</v>
       </c>
       <c r="B225" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26247,7 +26247,7 @@
         <v>135300543</v>
       </c>
       <c r="B226" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -26475,7 +26475,7 @@
         <v>135294360</v>
       </c>
       <c r="B228" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -26597,7 +26597,7 @@
         <v>135294810</v>
       </c>
       <c r="B229" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -26718,7 +26718,7 @@
         <v>135298406</v>
       </c>
       <c r="B230" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -26847,7 +26847,7 @@
         <v>135298438</v>
       </c>
       <c r="B231" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -26963,7 +26963,7 @@
         <v>135298440</v>
       </c>
       <c r="B232" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -27084,7 +27084,7 @@
         <v>135298445</v>
       </c>
       <c r="B233" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -27205,7 +27205,7 @@
         <v>135300490</v>
       </c>
       <c r="B234" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -27326,7 +27326,7 @@
         <v>135300553</v>
       </c>
       <c r="B235" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>135300563</v>
       </c>
       <c r="B236" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -27568,7 +27568,7 @@
         <v>135300567</v>
       </c>
       <c r="B237" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>135294832</v>
       </c>
       <c r="B239" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -27911,7 +27911,7 @@
         <v>135301755</v>
       </c>
       <c r="B240" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -28027,7 +28027,7 @@
         <v>135294377</v>
       </c>
       <c r="B241" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -28148,7 +28148,7 @@
         <v>135300538</v>
       </c>
       <c r="B242" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -28273,7 +28273,7 @@
         <v>135301738</v>
       </c>
       <c r="B243" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -28394,7 +28394,7 @@
         <v>135300501</v>
       </c>
       <c r="B244" t="n">
-        <v>56706</v>
+        <v>56711</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -28510,7 +28510,7 @@
         <v>135301756</v>
       </c>
       <c r="B245" t="n">
-        <v>111153</v>
+        <v>111210</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -28626,7 +28626,7 @@
         <v>135294816</v>
       </c>
       <c r="B246" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -28742,7 +28742,7 @@
         <v>135301744</v>
       </c>
       <c r="B247" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -28858,7 +28858,7 @@
         <v>135294825</v>
       </c>
       <c r="B248" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -28974,7 +28974,7 @@
         <v>135294841</v>
       </c>
       <c r="B249" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29090,7 +29090,7 @@
         <v>135300497</v>
       </c>
       <c r="B250" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>135301741</v>
       </c>
       <c r="B251" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29322,7 +29322,7 @@
         <v>135301757</v>
       </c>
       <c r="B252" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29438,7 +29438,7 @@
         <v>135301766</v>
       </c>
       <c r="B253" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -29554,7 +29554,7 @@
         <v>135301770</v>
       </c>
       <c r="B254" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>135301790</v>
       </c>
       <c r="B255" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -29786,7 +29786,7 @@
         <v>135298442</v>
       </c>
       <c r="B256" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -29902,7 +29902,7 @@
         <v>135301747</v>
       </c>
       <c r="B257" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -30018,7 +30018,7 @@
         <v>135301759</v>
       </c>
       <c r="B258" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30134,7 +30134,7 @@
         <v>135295146</v>
       </c>
       <c r="B259" t="n">
-        <v>100806</v>
+        <v>100854</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -30454,7 +30454,7 @@
         <v>135298444</v>
       </c>
       <c r="B262" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -30570,7 +30570,7 @@
         <v>135298446</v>
       </c>
       <c r="B263" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -30686,7 +30686,7 @@
         <v>135300488</v>
       </c>
       <c r="B264" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -30802,7 +30802,7 @@
         <v>135300493</v>
       </c>
       <c r="B265" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -30918,7 +30918,7 @@
         <v>135300550</v>
       </c>
       <c r="B266" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -31034,7 +31034,7 @@
         <v>135301752</v>
       </c>
       <c r="B267" t="n">
-        <v>80438</v>
+        <v>80476</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -31252,7 +31252,7 @@
         <v>135294785</v>
       </c>
       <c r="B269" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -31368,7 +31368,7 @@
         <v>135294801</v>
       </c>
       <c r="B270" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -31484,7 +31484,7 @@
         <v>135294812</v>
       </c>
       <c r="B271" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -31600,7 +31600,7 @@
         <v>135294826</v>
       </c>
       <c r="B272" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -31716,7 +31716,7 @@
         <v>135294833</v>
       </c>
       <c r="B273" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -31832,7 +31832,7 @@
         <v>135298403</v>
       </c>
       <c r="B274" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -31944,7 +31944,7 @@
         <v>135298407</v>
       </c>
       <c r="B275" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -32056,7 +32056,7 @@
         <v>135300489</v>
       </c>
       <c r="B276" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -32172,7 +32172,7 @@
         <v>135300491</v>
       </c>
       <c r="B277" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -32288,7 +32288,7 @@
         <v>135300524</v>
       </c>
       <c r="B278" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -32404,7 +32404,7 @@
         <v>135300528</v>
       </c>
       <c r="B279" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -32520,7 +32520,7 @@
         <v>135300533</v>
       </c>
       <c r="B280" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>135300539</v>
       </c>
       <c r="B281" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -32752,7 +32752,7 @@
         <v>135300546</v>
       </c>
       <c r="B282" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -32868,7 +32868,7 @@
         <v>135300549</v>
       </c>
       <c r="B283" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>135300554</v>
       </c>
       <c r="B284" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -33100,7 +33100,7 @@
         <v>135300557</v>
       </c>
       <c r="B285" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -33216,7 +33216,7 @@
         <v>135300564</v>
       </c>
       <c r="B286" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>135301787</v>
       </c>
       <c r="B287" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -33448,7 +33448,7 @@
         <v>135291042</v>
       </c>
       <c r="B288" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>135294362</v>
       </c>
       <c r="B289" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -33672,7 +33672,7 @@
         <v>135294376</v>
       </c>
       <c r="B290" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>135294796</v>
       </c>
       <c r="B291" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -33900,7 +33900,7 @@
         <v>135294828</v>
       </c>
       <c r="B292" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -34016,7 +34016,7 @@
         <v>135294831</v>
       </c>
       <c r="B293" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -34132,7 +34132,7 @@
         <v>135294835</v>
       </c>
       <c r="B294" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -34248,7 +34248,7 @@
         <v>135300505</v>
       </c>
       <c r="B295" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -34369,7 +34369,7 @@
         <v>135301765</v>
       </c>
       <c r="B296" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -34485,7 +34485,7 @@
         <v>135301773</v>
       </c>
       <c r="B297" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>

--- a/artfynd/A 26089-2024 artfynd.xlsx
+++ b/artfynd/A 26089-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135295377</v>
       </c>
       <c r="B3" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>135294352</v>
       </c>
       <c r="B4" t="n">
-        <v>92411</v>
+        <v>92438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135294350</v>
       </c>
       <c r="B6" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>135294354</v>
       </c>
       <c r="B7" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>135294783</v>
       </c>
       <c r="B8" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>135294850</v>
       </c>
       <c r="B9" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>135294854</v>
       </c>
       <c r="B10" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>135295381</v>
       </c>
       <c r="B11" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>135295383</v>
       </c>
       <c r="B12" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>135300485</v>
       </c>
       <c r="B13" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>135300572</v>
       </c>
       <c r="B14" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>135301725</v>
       </c>
       <c r="B15" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>135301737</v>
       </c>
       <c r="B16" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>135301777</v>
       </c>
       <c r="B17" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>135301793</v>
       </c>
       <c r="B18" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>135294795</v>
       </c>
       <c r="B19" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>135301800</v>
       </c>
       <c r="B20" t="n">
-        <v>81393</v>
+        <v>81420</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>135300576</v>
       </c>
       <c r="B22" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>135294851</v>
       </c>
       <c r="B25" t="n">
-        <v>91039</v>
+        <v>91066</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>135301730</v>
       </c>
       <c r="B27" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>135294359</v>
       </c>
       <c r="B28" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>135294852</v>
       </c>
       <c r="B29" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>135294351</v>
       </c>
       <c r="B31" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135301732</v>
       </c>
       <c r="B32" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>135301797</v>
       </c>
       <c r="B33" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>135294358</v>
       </c>
       <c r="B34" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>135295380</v>
       </c>
       <c r="B36" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         <v>135294782</v>
       </c>
       <c r="B38" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>135294787</v>
       </c>
       <c r="B39" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>135294788</v>
       </c>
       <c r="B40" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>135294790</v>
       </c>
       <c r="B41" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>135294794</v>
       </c>
       <c r="B42" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>135294836</v>
       </c>
       <c r="B43" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>135294847</v>
       </c>
       <c r="B44" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>135294849</v>
       </c>
       <c r="B45" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>135295388</v>
       </c>
       <c r="B46" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>135301733</v>
       </c>
       <c r="B47" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>135301780</v>
       </c>
       <c r="B48" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>135294357</v>
       </c>
       <c r="B54" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>135294781</v>
       </c>
       <c r="B55" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         <v>135294843</v>
       </c>
       <c r="B56" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>135295389</v>
       </c>
       <c r="B57" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>135301728</v>
       </c>
       <c r="B58" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>135301791</v>
       </c>
       <c r="B59" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>135295379</v>
       </c>
       <c r="B60" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>135301778</v>
       </c>
       <c r="B61" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7628,7 +7628,7 @@
         <v>135301796</v>
       </c>
       <c r="B62" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>135294355</v>
       </c>
       <c r="B63" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>135295378</v>
       </c>
       <c r="B64" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>135295386</v>
       </c>
       <c r="B65" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>135295387</v>
       </c>
       <c r="B66" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>135300574</v>
       </c>
       <c r="B67" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>135300575</v>
       </c>
       <c r="B68" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>135301794</v>
       </c>
       <c r="B69" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         <v>135294356</v>
       </c>
       <c r="B70" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>135294853</v>
       </c>
       <c r="B71" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>135295384</v>
       </c>
       <c r="B72" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>135295385</v>
       </c>
       <c r="B73" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>135301727</v>
       </c>
       <c r="B74" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>135301735</v>
       </c>
       <c r="B75" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>135295442</v>
       </c>
       <c r="B76" t="n">
-        <v>93334</v>
+        <v>93361</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         <v>135301801</v>
       </c>
       <c r="B77" t="n">
-        <v>93334</v>
+        <v>93361</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>135300502</v>
       </c>
       <c r="B78" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>135294364</v>
       </c>
       <c r="B83" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>135294374</v>
       </c>
       <c r="B84" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>135294791</v>
       </c>
       <c r="B85" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         <v>135294800</v>
       </c>
       <c r="B86" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10457,7 +10457,7 @@
         <v>135294823</v>
       </c>
       <c r="B87" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>135294824</v>
       </c>
       <c r="B88" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>135294837</v>
       </c>
       <c r="B89" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>135298434</v>
       </c>
       <c r="B90" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>135298439</v>
       </c>
       <c r="B91" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>135298457</v>
       </c>
       <c r="B92" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>135298458</v>
       </c>
       <c r="B93" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>135300494</v>
       </c>
       <c r="B94" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         <v>135300500</v>
       </c>
       <c r="B95" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>135300504</v>
       </c>
       <c r="B96" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>135300508</v>
       </c>
       <c r="B97" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11738,7 +11738,7 @@
         <v>135300511</v>
       </c>
       <c r="B98" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>135300526</v>
       </c>
       <c r="B99" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
         <v>135300531</v>
       </c>
       <c r="B100" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12091,7 +12091,7 @@
         <v>135300534</v>
       </c>
       <c r="B101" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>135300537</v>
       </c>
       <c r="B102" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12328,7 +12328,7 @@
         <v>135300541</v>
       </c>
       <c r="B103" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>135300552</v>
       </c>
       <c r="B104" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>135300555</v>
       </c>
       <c r="B105" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>135300560</v>
       </c>
       <c r="B106" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12792,7 +12792,7 @@
         <v>135300561</v>
       </c>
       <c r="B107" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>135300562</v>
       </c>
       <c r="B108" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>135300568</v>
       </c>
       <c r="B109" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>135300569</v>
       </c>
       <c r="B110" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>135301768</v>
       </c>
       <c r="B111" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         <v>135294811</v>
       </c>
       <c r="B112" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13493,7 +13493,7 @@
         <v>135300523</v>
       </c>
       <c r="B113" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>135301784</v>
       </c>
       <c r="B114" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>135300510</v>
       </c>
       <c r="B115" t="n">
-        <v>81393</v>
+        <v>81420</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>135294361</v>
       </c>
       <c r="B117" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>135295390</v>
       </c>
       <c r="B118" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>135298393</v>
       </c>
       <c r="B119" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>135298394</v>
       </c>
       <c r="B120" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>135298401</v>
       </c>
       <c r="B121" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>135298436</v>
       </c>
       <c r="B122" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14644,7 +14644,7 @@
         <v>135298437</v>
       </c>
       <c r="B123" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>135300514</v>
       </c>
       <c r="B124" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14876,7 +14876,7 @@
         <v>135300540</v>
       </c>
       <c r="B125" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>135300566</v>
       </c>
       <c r="B126" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>135294365</v>
       </c>
       <c r="B130" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>135300496</v>
       </c>
       <c r="B131" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>135300513</v>
       </c>
       <c r="B132" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15758,7 +15758,7 @@
         <v>135300516</v>
       </c>
       <c r="B133" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>135300519</v>
       </c>
       <c r="B134" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         <v>135300542</v>
       </c>
       <c r="B136" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>135294829</v>
       </c>
       <c r="B137" t="n">
-        <v>93307</v>
+        <v>93334</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>135294363</v>
       </c>
       <c r="B138" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16441,7 +16441,7 @@
         <v>135294839</v>
       </c>
       <c r="B139" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16557,7 +16557,7 @@
         <v>135298447</v>
       </c>
       <c r="B140" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>135301769</v>
       </c>
       <c r="B141" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16794,7 +16794,7 @@
         <v>135301776</v>
       </c>
       <c r="B142" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>135301781</v>
       </c>
       <c r="B143" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17036,7 +17036,7 @@
         <v>135301740</v>
       </c>
       <c r="B144" t="n">
-        <v>93317</v>
+        <v>93344</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>135300495</v>
       </c>
       <c r="B145" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17370,7 +17370,7 @@
         <v>135300520</v>
       </c>
       <c r="B147" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17690,7 +17690,7 @@
         <v>135294797</v>
       </c>
       <c r="B150" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17806,7 +17806,7 @@
         <v>135298397</v>
       </c>
       <c r="B151" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
         <v>135298398</v>
       </c>
       <c r="B152" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18038,7 +18038,7 @@
         <v>135298433</v>
       </c>
       <c r="B153" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>135300487</v>
       </c>
       <c r="B154" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         <v>135300509</v>
       </c>
       <c r="B155" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>135300525</v>
       </c>
       <c r="B156" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18502,7 +18502,7 @@
         <v>135300529</v>
       </c>
       <c r="B157" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>135294821</v>
       </c>
       <c r="B165" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19448,7 +19448,7 @@
         <v>135298443</v>
       </c>
       <c r="B166" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19564,7 +19564,7 @@
         <v>135300507</v>
       </c>
       <c r="B167" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19680,7 +19680,7 @@
         <v>135300515</v>
       </c>
       <c r="B168" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>135300521</v>
       </c>
       <c r="B169" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>135301762</v>
       </c>
       <c r="B170" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20436,7 +20436,7 @@
         <v>135294373</v>
       </c>
       <c r="B175" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20548,7 +20548,7 @@
         <v>135294375</v>
       </c>
       <c r="B176" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         <v>135294784</v>
       </c>
       <c r="B177" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>135294799</v>
       </c>
       <c r="B178" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20892,7 +20892,7 @@
         <v>135294813</v>
       </c>
       <c r="B179" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>135294818</v>
       </c>
       <c r="B180" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21124,7 +21124,7 @@
         <v>135294820</v>
       </c>
       <c r="B181" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21240,7 +21240,7 @@
         <v>135294827</v>
       </c>
       <c r="B182" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21356,7 +21356,7 @@
         <v>135294830</v>
       </c>
       <c r="B183" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21472,7 +21472,7 @@
         <v>135294834</v>
       </c>
       <c r="B184" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21588,7 +21588,7 @@
         <v>135294840</v>
       </c>
       <c r="B185" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21704,7 +21704,7 @@
         <v>135298391</v>
       </c>
       <c r="B186" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>135298435</v>
       </c>
       <c r="B187" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21932,7 +21932,7 @@
         <v>135298459</v>
       </c>
       <c r="B188" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22048,7 +22048,7 @@
         <v>135300492</v>
       </c>
       <c r="B189" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>135300498</v>
       </c>
       <c r="B190" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>135300503</v>
       </c>
       <c r="B191" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22396,7 +22396,7 @@
         <v>135300517</v>
       </c>
       <c r="B192" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>135300530</v>
       </c>
       <c r="B193" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -22628,7 +22628,7 @@
         <v>135300532</v>
       </c>
       <c r="B194" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>135300536</v>
       </c>
       <c r="B195" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -22860,7 +22860,7 @@
         <v>135300547</v>
       </c>
       <c r="B196" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22976,7 +22976,7 @@
         <v>135300548</v>
       </c>
       <c r="B197" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23092,7 +23092,7 @@
         <v>135300551</v>
       </c>
       <c r="B198" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23208,7 +23208,7 @@
         <v>135300565</v>
       </c>
       <c r="B199" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>135301743</v>
       </c>
       <c r="B200" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23440,7 +23440,7 @@
         <v>135301764</v>
       </c>
       <c r="B201" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>135301774</v>
       </c>
       <c r="B202" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -23672,7 +23672,7 @@
         <v>135301783</v>
       </c>
       <c r="B203" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -23788,7 +23788,7 @@
         <v>135301786</v>
       </c>
       <c r="B204" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23904,7 +23904,7 @@
         <v>135301788</v>
       </c>
       <c r="B205" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24020,7 +24020,7 @@
         <v>135300544</v>
       </c>
       <c r="B206" t="n">
-        <v>80420</v>
+        <v>80447</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
         <v>135300545</v>
       </c>
       <c r="B207" t="n">
-        <v>80420</v>
+        <v>80447</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>135294793</v>
       </c>
       <c r="B208" t="n">
-        <v>80530</v>
+        <v>80557</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>135294807</v>
       </c>
       <c r="B211" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>135294815</v>
       </c>
       <c r="B212" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>135301748</v>
       </c>
       <c r="B213" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>135294805</v>
       </c>
       <c r="B216" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25240,7 +25240,7 @@
         <v>135301749</v>
       </c>
       <c r="B217" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25356,7 +25356,7 @@
         <v>135301754</v>
       </c>
       <c r="B218" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25574,7 +25574,7 @@
         <v>135301751</v>
       </c>
       <c r="B220" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -25894,7 +25894,7 @@
         <v>135300527</v>
       </c>
       <c r="B223" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -28510,7 +28510,7 @@
         <v>135301756</v>
       </c>
       <c r="B245" t="n">
-        <v>111210</v>
+        <v>111237</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -28626,7 +28626,7 @@
         <v>135294816</v>
       </c>
       <c r="B246" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -28742,7 +28742,7 @@
         <v>135301744</v>
       </c>
       <c r="B247" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -28858,7 +28858,7 @@
         <v>135294825</v>
       </c>
       <c r="B248" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -28974,7 +28974,7 @@
         <v>135294841</v>
       </c>
       <c r="B249" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29090,7 +29090,7 @@
         <v>135300497</v>
       </c>
       <c r="B250" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>135301741</v>
       </c>
       <c r="B251" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29322,7 +29322,7 @@
         <v>135301757</v>
       </c>
       <c r="B252" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29438,7 +29438,7 @@
         <v>135301766</v>
       </c>
       <c r="B253" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -29554,7 +29554,7 @@
         <v>135301770</v>
       </c>
       <c r="B254" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>135301790</v>
       </c>
       <c r="B255" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -29786,7 +29786,7 @@
         <v>135298442</v>
       </c>
       <c r="B256" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -29902,7 +29902,7 @@
         <v>135301747</v>
       </c>
       <c r="B257" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -30018,7 +30018,7 @@
         <v>135301759</v>
       </c>
       <c r="B258" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30134,7 +30134,7 @@
         <v>135295146</v>
       </c>
       <c r="B259" t="n">
-        <v>100854</v>
+        <v>100881</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -30454,7 +30454,7 @@
         <v>135298444</v>
       </c>
       <c r="B262" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -30570,7 +30570,7 @@
         <v>135298446</v>
       </c>
       <c r="B263" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -30686,7 +30686,7 @@
         <v>135300488</v>
       </c>
       <c r="B264" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -30802,7 +30802,7 @@
         <v>135300493</v>
       </c>
       <c r="B265" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -30918,7 +30918,7 @@
         <v>135300550</v>
       </c>
       <c r="B266" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -31034,7 +31034,7 @@
         <v>135301752</v>
       </c>
       <c r="B267" t="n">
-        <v>80476</v>
+        <v>80503</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -31252,7 +31252,7 @@
         <v>135294785</v>
       </c>
       <c r="B269" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -31368,7 +31368,7 @@
         <v>135294801</v>
       </c>
       <c r="B270" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -31484,7 +31484,7 @@
         <v>135294812</v>
       </c>
       <c r="B271" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -31600,7 +31600,7 @@
         <v>135294826</v>
       </c>
       <c r="B272" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -31716,7 +31716,7 @@
         <v>135294833</v>
       </c>
       <c r="B273" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -31832,7 +31832,7 @@
         <v>135298403</v>
       </c>
       <c r="B274" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -31944,7 +31944,7 @@
         <v>135298407</v>
       </c>
       <c r="B275" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -32056,7 +32056,7 @@
         <v>135300489</v>
       </c>
       <c r="B276" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -32172,7 +32172,7 @@
         <v>135300491</v>
       </c>
       <c r="B277" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -32288,7 +32288,7 @@
         <v>135300524</v>
       </c>
       <c r="B278" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -32404,7 +32404,7 @@
         <v>135300528</v>
       </c>
       <c r="B279" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -32520,7 +32520,7 @@
         <v>135300533</v>
       </c>
       <c r="B280" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>135300539</v>
       </c>
       <c r="B281" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -32752,7 +32752,7 @@
         <v>135300546</v>
       </c>
       <c r="B282" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -32868,7 +32868,7 @@
         <v>135300549</v>
       </c>
       <c r="B283" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>135300554</v>
       </c>
       <c r="B284" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -33100,7 +33100,7 @@
         <v>135300557</v>
       </c>
       <c r="B285" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -33216,7 +33216,7 @@
         <v>135300564</v>
       </c>
       <c r="B286" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>135301787</v>
       </c>
       <c r="B287" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -33448,7 +33448,7 @@
         <v>135291042</v>
       </c>
       <c r="B288" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>135294362</v>
       </c>
       <c r="B289" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -33672,7 +33672,7 @@
         <v>135294376</v>
       </c>
       <c r="B290" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>135294796</v>
       </c>
       <c r="B291" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -33900,7 +33900,7 @@
         <v>135294828</v>
       </c>
       <c r="B292" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -34016,7 +34016,7 @@
         <v>135294831</v>
       </c>
       <c r="B293" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -34132,7 +34132,7 @@
         <v>135294835</v>
       </c>
       <c r="B294" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -34248,7 +34248,7 @@
         <v>135300505</v>
       </c>
       <c r="B295" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -34369,7 +34369,7 @@
         <v>135301765</v>
       </c>
       <c r="B296" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -34485,7 +34485,7 @@
         <v>135301773</v>
       </c>
       <c r="B297" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>

--- a/artfynd/A 26089-2024 artfynd.xlsx
+++ b/artfynd/A 26089-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135295377</v>
       </c>
       <c r="B3" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>135294352</v>
       </c>
       <c r="B4" t="n">
-        <v>92443</v>
+        <v>92445</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>135300576</v>
       </c>
       <c r="B22" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>135294851</v>
       </c>
       <c r="B25" t="n">
-        <v>91069</v>
+        <v>91071</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>135301730</v>
       </c>
       <c r="B27" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>135294359</v>
       </c>
       <c r="B28" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>135294852</v>
       </c>
       <c r="B29" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>135294351</v>
       </c>
       <c r="B31" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135301732</v>
       </c>
       <c r="B32" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>135301797</v>
       </c>
       <c r="B33" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>135294357</v>
       </c>
       <c r="B54" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>135294781</v>
       </c>
       <c r="B55" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         <v>135294843</v>
       </c>
       <c r="B56" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>135295389</v>
       </c>
       <c r="B57" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>135301728</v>
       </c>
       <c r="B58" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>135301791</v>
       </c>
       <c r="B59" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>135295442</v>
       </c>
       <c r="B76" t="n">
-        <v>93366</v>
+        <v>93368</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         <v>135301801</v>
       </c>
       <c r="B77" t="n">
-        <v>93366</v>
+        <v>93368</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>135300502</v>
       </c>
       <c r="B78" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         <v>135294811</v>
       </c>
       <c r="B112" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>135294361</v>
       </c>
       <c r="B117" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>135295390</v>
       </c>
       <c r="B118" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>135298393</v>
       </c>
       <c r="B119" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>135298394</v>
       </c>
       <c r="B120" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>135298401</v>
       </c>
       <c r="B121" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>135298436</v>
       </c>
       <c r="B122" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14644,7 +14644,7 @@
         <v>135298437</v>
       </c>
       <c r="B123" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>135300514</v>
       </c>
       <c r="B124" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14876,7 +14876,7 @@
         <v>135300540</v>
       </c>
       <c r="B125" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>135300566</v>
       </c>
       <c r="B126" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>135294365</v>
       </c>
       <c r="B130" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>135300496</v>
       </c>
       <c r="B131" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>135300513</v>
       </c>
       <c r="B132" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15758,7 +15758,7 @@
         <v>135300516</v>
       </c>
       <c r="B133" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>135300519</v>
       </c>
       <c r="B134" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         <v>135300542</v>
       </c>
       <c r="B136" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>135294829</v>
       </c>
       <c r="B137" t="n">
-        <v>93339</v>
+        <v>93341</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>135294363</v>
       </c>
       <c r="B138" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16441,7 +16441,7 @@
         <v>135294839</v>
       </c>
       <c r="B139" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16557,7 +16557,7 @@
         <v>135298447</v>
       </c>
       <c r="B140" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>135301769</v>
       </c>
       <c r="B141" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16794,7 +16794,7 @@
         <v>135301776</v>
       </c>
       <c r="B142" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>135301781</v>
       </c>
       <c r="B143" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17036,7 +17036,7 @@
         <v>135301740</v>
       </c>
       <c r="B144" t="n">
-        <v>93349</v>
+        <v>93351</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>135300495</v>
       </c>
       <c r="B145" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -28510,7 +28510,7 @@
         <v>135301756</v>
       </c>
       <c r="B245" t="n">
-        <v>111242</v>
+        <v>111244</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -28626,7 +28626,7 @@
         <v>135294816</v>
       </c>
       <c r="B246" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -28742,7 +28742,7 @@
         <v>135301744</v>
       </c>
       <c r="B247" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -28858,7 +28858,7 @@
         <v>135294825</v>
       </c>
       <c r="B248" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -28974,7 +28974,7 @@
         <v>135294841</v>
       </c>
       <c r="B249" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29090,7 +29090,7 @@
         <v>135300497</v>
       </c>
       <c r="B250" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>135301741</v>
       </c>
       <c r="B251" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29322,7 +29322,7 @@
         <v>135301757</v>
       </c>
       <c r="B252" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29438,7 +29438,7 @@
         <v>135301766</v>
       </c>
       <c r="B253" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -29554,7 +29554,7 @@
         <v>135301770</v>
       </c>
       <c r="B254" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>135301790</v>
       </c>
       <c r="B255" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -29786,7 +29786,7 @@
         <v>135298442</v>
       </c>
       <c r="B256" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -29902,7 +29902,7 @@
         <v>135301747</v>
       </c>
       <c r="B257" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -30018,7 +30018,7 @@
         <v>135301759</v>
       </c>
       <c r="B258" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30134,7 +30134,7 @@
         <v>135295146</v>
       </c>
       <c r="B259" t="n">
-        <v>100886</v>
+        <v>100888</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>

--- a/artfynd/A 26089-2024 artfynd.xlsx
+++ b/artfynd/A 26089-2024 artfynd.xlsx
@@ -9245,7 +9245,7 @@
         <v>135295442</v>
       </c>
       <c r="B76" t="n">
-        <v>93368</v>
+        <v>93383</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
